--- a/outputs/Custom_Drug_MANDOROS_Master_Report_CORRECTED.xlsx
+++ b/outputs/Custom_Drug_MANDOROS_Master_Report_CORRECTED.xlsx
@@ -146,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -168,11 +168,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,6 +270,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -300,6 +346,606 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>280</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>23</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>40</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -881,308 +1527,308 @@
           <t>STUDY &amp; INTERVENTION ARMS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="25" t="n"/>
+      <c r="H1" s="25" t="n"/>
+      <c r="I1" s="25" t="n"/>
+      <c r="J1" s="25" t="n"/>
+      <c r="K1" s="25" t="n"/>
+      <c r="L1" s="26" t="n"/>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>INCLUSION CRITERIA</t>
         </is>
       </c>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
+      <c r="N1" s="25" t="n"/>
+      <c r="O1" s="25" t="n"/>
+      <c r="P1" s="25" t="n"/>
+      <c r="Q1" s="25" t="n"/>
+      <c r="R1" s="25" t="n"/>
+      <c r="S1" s="25" t="n"/>
+      <c r="T1" s="25" t="n"/>
+      <c r="U1" s="25" t="n"/>
+      <c r="V1" s="25" t="n"/>
+      <c r="W1" s="25" t="n"/>
+      <c r="X1" s="25" t="n"/>
+      <c r="Y1" s="25" t="n"/>
+      <c r="Z1" s="26" t="n"/>
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>EXCLUSION CRITERIA</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
-      <c r="AE1" s="1" t="n"/>
-      <c r="AF1" s="1" t="n"/>
-      <c r="AG1" s="1" t="n"/>
-      <c r="AH1" s="1" t="n"/>
-      <c r="AI1" s="1" t="n"/>
-      <c r="AJ1" s="1" t="n"/>
-      <c r="AK1" s="1" t="n"/>
+      <c r="AB1" s="25" t="n"/>
+      <c r="AC1" s="25" t="n"/>
+      <c r="AD1" s="25" t="n"/>
+      <c r="AE1" s="25" t="n"/>
+      <c r="AF1" s="25" t="n"/>
+      <c r="AG1" s="25" t="n"/>
+      <c r="AH1" s="25" t="n"/>
+      <c r="AI1" s="25" t="n"/>
+      <c r="AJ1" s="25" t="n"/>
+      <c r="AK1" s="26" t="n"/>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>POPULATION STRATIFICATION</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="n"/>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
-      <c r="AS1" s="1" t="n"/>
+      <c r="AM1" s="25" t="n"/>
+      <c r="AN1" s="25" t="n"/>
+      <c r="AO1" s="25" t="n"/>
+      <c r="AP1" s="25" t="n"/>
+      <c r="AQ1" s="25" t="n"/>
+      <c r="AR1" s="25" t="n"/>
+      <c r="AS1" s="26" t="n"/>
       <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>BASELINE CHARACTERISTICS &amp; LABS (TIME 0)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="n"/>
-      <c r="AV1" s="1" t="n"/>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="n"/>
-      <c r="AY1" s="1" t="n"/>
-      <c r="AZ1" s="1" t="n"/>
-      <c r="BA1" s="1" t="n"/>
-      <c r="BB1" s="1" t="n"/>
-      <c r="BC1" s="1" t="n"/>
-      <c r="BD1" s="1" t="n"/>
-      <c r="BE1" s="1" t="n"/>
-      <c r="BF1" s="1" t="n"/>
-      <c r="BG1" s="1" t="n"/>
-      <c r="BH1" s="1" t="n"/>
-      <c r="BI1" s="1" t="n"/>
-      <c r="BJ1" s="1" t="n"/>
-      <c r="BK1" s="1" t="n"/>
-      <c r="BL1" s="1" t="n"/>
-      <c r="BM1" s="1" t="n"/>
-      <c r="BN1" s="1" t="n"/>
-      <c r="BO1" s="1" t="n"/>
-      <c r="BP1" s="1" t="n"/>
-      <c r="BQ1" s="1" t="n"/>
-      <c r="BR1" s="1" t="n"/>
-      <c r="BS1" s="1" t="n"/>
-      <c r="BT1" s="1" t="n"/>
-      <c r="BU1" s="1" t="n"/>
-      <c r="BV1" s="1" t="n"/>
-      <c r="BW1" s="1" t="n"/>
-      <c r="BX1" s="1" t="n"/>
-      <c r="BY1" s="1" t="n"/>
-      <c r="BZ1" s="1" t="n"/>
-      <c r="CA1" s="1" t="n"/>
-      <c r="CB1" s="1" t="n"/>
-      <c r="CC1" s="1" t="n"/>
-      <c r="CD1" s="1" t="n"/>
-      <c r="CE1" s="1" t="n"/>
-      <c r="CF1" s="1" t="n"/>
-      <c r="CG1" s="1" t="n"/>
-      <c r="CH1" s="1" t="n"/>
-      <c r="CI1" s="1" t="n"/>
-      <c r="CJ1" s="1" t="n"/>
-      <c r="CK1" s="1" t="n"/>
-      <c r="CL1" s="1" t="n"/>
-      <c r="CM1" s="1" t="n"/>
-      <c r="CN1" s="1" t="n"/>
-      <c r="CO1" s="1" t="n"/>
-      <c r="CP1" s="1" t="n"/>
-      <c r="CQ1" s="1" t="n"/>
-      <c r="CR1" s="1" t="n"/>
-      <c r="CS1" s="1" t="n"/>
-      <c r="CT1" s="1" t="n"/>
-      <c r="CU1" s="1" t="n"/>
-      <c r="CV1" s="1" t="n"/>
-      <c r="CW1" s="1" t="n"/>
-      <c r="CX1" s="1" t="n"/>
-      <c r="CY1" s="1" t="n"/>
-      <c r="CZ1" s="1" t="n"/>
-      <c r="DA1" s="1" t="n"/>
-      <c r="DB1" s="1" t="n"/>
-      <c r="DC1" s="1" t="n"/>
-      <c r="DD1" s="1" t="n"/>
-      <c r="DE1" s="1" t="n"/>
-      <c r="DF1" s="1" t="n"/>
-      <c r="DG1" s="1" t="n"/>
-      <c r="DH1" s="1" t="n"/>
-      <c r="DI1" s="1" t="n"/>
-      <c r="DJ1" s="1" t="n"/>
-      <c r="DK1" s="1" t="n"/>
-      <c r="DL1" s="1" t="n"/>
-      <c r="DM1" s="1" t="n"/>
-      <c r="DN1" s="1" t="n"/>
-      <c r="DO1" s="1" t="n"/>
-      <c r="DP1" s="1" t="n"/>
-      <c r="DQ1" s="1" t="n"/>
-      <c r="DR1" s="1" t="n"/>
-      <c r="DS1" s="1" t="n"/>
-      <c r="DT1" s="1" t="n"/>
-      <c r="DU1" s="1" t="n"/>
-      <c r="DV1" s="1" t="n"/>
-      <c r="DW1" s="1" t="n"/>
-      <c r="DX1" s="1" t="n"/>
-      <c r="DY1" s="1" t="n"/>
-      <c r="DZ1" s="1" t="n"/>
-      <c r="EA1" s="1" t="n"/>
-      <c r="EB1" s="1" t="n"/>
-      <c r="EC1" s="1" t="n"/>
-      <c r="ED1" s="1" t="n"/>
-      <c r="EE1" s="1" t="n"/>
-      <c r="EF1" s="1" t="n"/>
-      <c r="EG1" s="1" t="n"/>
-      <c r="EH1" s="1" t="n"/>
-      <c r="EI1" s="1" t="n"/>
-      <c r="EJ1" s="1" t="n"/>
-      <c r="EK1" s="1" t="n"/>
-      <c r="EL1" s="1" t="n"/>
-      <c r="EM1" s="1" t="n"/>
-      <c r="EN1" s="1" t="n"/>
-      <c r="EO1" s="1" t="n"/>
-      <c r="EP1" s="1" t="n"/>
-      <c r="EQ1" s="1" t="n"/>
-      <c r="ER1" s="1" t="n"/>
-      <c r="ES1" s="1" t="n"/>
-      <c r="ET1" s="1" t="n"/>
-      <c r="EU1" s="1" t="n"/>
-      <c r="EV1" s="1" t="n"/>
-      <c r="EW1" s="1" t="n"/>
-      <c r="EX1" s="1" t="n"/>
-      <c r="EY1" s="1" t="n"/>
-      <c r="EZ1" s="1" t="n"/>
-      <c r="FA1" s="1" t="n"/>
-      <c r="FB1" s="1" t="n"/>
-      <c r="FC1" s="1" t="n"/>
-      <c r="FD1" s="1" t="n"/>
-      <c r="FE1" s="1" t="n"/>
-      <c r="FF1" s="1" t="n"/>
-      <c r="FG1" s="1" t="n"/>
-      <c r="FH1" s="1" t="n"/>
-      <c r="FI1" s="1" t="n"/>
+      <c r="AU1" s="25" t="n"/>
+      <c r="AV1" s="25" t="n"/>
+      <c r="AW1" s="25" t="n"/>
+      <c r="AX1" s="25" t="n"/>
+      <c r="AY1" s="25" t="n"/>
+      <c r="AZ1" s="25" t="n"/>
+      <c r="BA1" s="25" t="n"/>
+      <c r="BB1" s="25" t="n"/>
+      <c r="BC1" s="25" t="n"/>
+      <c r="BD1" s="25" t="n"/>
+      <c r="BE1" s="25" t="n"/>
+      <c r="BF1" s="25" t="n"/>
+      <c r="BG1" s="25" t="n"/>
+      <c r="BH1" s="25" t="n"/>
+      <c r="BI1" s="25" t="n"/>
+      <c r="BJ1" s="25" t="n"/>
+      <c r="BK1" s="25" t="n"/>
+      <c r="BL1" s="25" t="n"/>
+      <c r="BM1" s="25" t="n"/>
+      <c r="BN1" s="25" t="n"/>
+      <c r="BO1" s="25" t="n"/>
+      <c r="BP1" s="25" t="n"/>
+      <c r="BQ1" s="25" t="n"/>
+      <c r="BR1" s="25" t="n"/>
+      <c r="BS1" s="25" t="n"/>
+      <c r="BT1" s="25" t="n"/>
+      <c r="BU1" s="25" t="n"/>
+      <c r="BV1" s="25" t="n"/>
+      <c r="BW1" s="25" t="n"/>
+      <c r="BX1" s="25" t="n"/>
+      <c r="BY1" s="25" t="n"/>
+      <c r="BZ1" s="25" t="n"/>
+      <c r="CA1" s="25" t="n"/>
+      <c r="CB1" s="25" t="n"/>
+      <c r="CC1" s="25" t="n"/>
+      <c r="CD1" s="25" t="n"/>
+      <c r="CE1" s="25" t="n"/>
+      <c r="CF1" s="25" t="n"/>
+      <c r="CG1" s="25" t="n"/>
+      <c r="CH1" s="25" t="n"/>
+      <c r="CI1" s="25" t="n"/>
+      <c r="CJ1" s="25" t="n"/>
+      <c r="CK1" s="25" t="n"/>
+      <c r="CL1" s="25" t="n"/>
+      <c r="CM1" s="25" t="n"/>
+      <c r="CN1" s="25" t="n"/>
+      <c r="CO1" s="25" t="n"/>
+      <c r="CP1" s="25" t="n"/>
+      <c r="CQ1" s="25" t="n"/>
+      <c r="CR1" s="25" t="n"/>
+      <c r="CS1" s="25" t="n"/>
+      <c r="CT1" s="25" t="n"/>
+      <c r="CU1" s="25" t="n"/>
+      <c r="CV1" s="25" t="n"/>
+      <c r="CW1" s="25" t="n"/>
+      <c r="CX1" s="25" t="n"/>
+      <c r="CY1" s="25" t="n"/>
+      <c r="CZ1" s="25" t="n"/>
+      <c r="DA1" s="25" t="n"/>
+      <c r="DB1" s="25" t="n"/>
+      <c r="DC1" s="25" t="n"/>
+      <c r="DD1" s="25" t="n"/>
+      <c r="DE1" s="25" t="n"/>
+      <c r="DF1" s="25" t="n"/>
+      <c r="DG1" s="25" t="n"/>
+      <c r="DH1" s="25" t="n"/>
+      <c r="DI1" s="25" t="n"/>
+      <c r="DJ1" s="25" t="n"/>
+      <c r="DK1" s="25" t="n"/>
+      <c r="DL1" s="25" t="n"/>
+      <c r="DM1" s="25" t="n"/>
+      <c r="DN1" s="25" t="n"/>
+      <c r="DO1" s="25" t="n"/>
+      <c r="DP1" s="25" t="n"/>
+      <c r="DQ1" s="25" t="n"/>
+      <c r="DR1" s="25" t="n"/>
+      <c r="DS1" s="25" t="n"/>
+      <c r="DT1" s="25" t="n"/>
+      <c r="DU1" s="25" t="n"/>
+      <c r="DV1" s="25" t="n"/>
+      <c r="DW1" s="25" t="n"/>
+      <c r="DX1" s="25" t="n"/>
+      <c r="DY1" s="25" t="n"/>
+      <c r="DZ1" s="25" t="n"/>
+      <c r="EA1" s="25" t="n"/>
+      <c r="EB1" s="25" t="n"/>
+      <c r="EC1" s="25" t="n"/>
+      <c r="ED1" s="25" t="n"/>
+      <c r="EE1" s="25" t="n"/>
+      <c r="EF1" s="25" t="n"/>
+      <c r="EG1" s="25" t="n"/>
+      <c r="EH1" s="25" t="n"/>
+      <c r="EI1" s="25" t="n"/>
+      <c r="EJ1" s="25" t="n"/>
+      <c r="EK1" s="25" t="n"/>
+      <c r="EL1" s="25" t="n"/>
+      <c r="EM1" s="25" t="n"/>
+      <c r="EN1" s="25" t="n"/>
+      <c r="EO1" s="25" t="n"/>
+      <c r="EP1" s="25" t="n"/>
+      <c r="EQ1" s="25" t="n"/>
+      <c r="ER1" s="25" t="n"/>
+      <c r="ES1" s="25" t="n"/>
+      <c r="ET1" s="25" t="n"/>
+      <c r="EU1" s="25" t="n"/>
+      <c r="EV1" s="25" t="n"/>
+      <c r="EW1" s="25" t="n"/>
+      <c r="EX1" s="25" t="n"/>
+      <c r="EY1" s="25" t="n"/>
+      <c r="EZ1" s="25" t="n"/>
+      <c r="FA1" s="25" t="n"/>
+      <c r="FB1" s="25" t="n"/>
+      <c r="FC1" s="25" t="n"/>
+      <c r="FD1" s="25" t="n"/>
+      <c r="FE1" s="25" t="n"/>
+      <c r="FF1" s="25" t="n"/>
+      <c r="FG1" s="25" t="n"/>
+      <c r="FH1" s="25" t="n"/>
+      <c r="FI1" s="26" t="n"/>
       <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>LONGITUDINAL EFFICACY &amp; ENDPOINTS (FOLLOW-UP)</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="n"/>
-      <c r="FL1" s="1" t="n"/>
-      <c r="FM1" s="1" t="n"/>
-      <c r="FN1" s="1" t="n"/>
-      <c r="FO1" s="1" t="n"/>
-      <c r="FP1" s="1" t="n"/>
-      <c r="FQ1" s="1" t="n"/>
-      <c r="FR1" s="1" t="n"/>
-      <c r="FS1" s="1" t="n"/>
-      <c r="FT1" s="1" t="n"/>
-      <c r="FU1" s="1" t="n"/>
-      <c r="FV1" s="1" t="n"/>
-      <c r="FW1" s="1" t="n"/>
-      <c r="FX1" s="1" t="n"/>
-      <c r="FY1" s="1" t="n"/>
-      <c r="FZ1" s="1" t="n"/>
-      <c r="GA1" s="1" t="n"/>
-      <c r="GB1" s="1" t="n"/>
-      <c r="GC1" s="1" t="n"/>
-      <c r="GD1" s="1" t="n"/>
-      <c r="GE1" s="1" t="n"/>
-      <c r="GF1" s="1" t="n"/>
-      <c r="GG1" s="1" t="n"/>
-      <c r="GH1" s="1" t="n"/>
-      <c r="GI1" s="1" t="n"/>
-      <c r="GJ1" s="1" t="n"/>
-      <c r="GK1" s="1" t="n"/>
-      <c r="GL1" s="1" t="n"/>
-      <c r="GM1" s="1" t="n"/>
-      <c r="GN1" s="1" t="n"/>
-      <c r="GO1" s="1" t="n"/>
-      <c r="GP1" s="1" t="n"/>
-      <c r="GQ1" s="1" t="n"/>
-      <c r="GR1" s="1" t="n"/>
-      <c r="GS1" s="1" t="n"/>
-      <c r="GT1" s="1" t="n"/>
-      <c r="GU1" s="1" t="n"/>
-      <c r="GV1" s="1" t="n"/>
-      <c r="GW1" s="1" t="n"/>
-      <c r="GX1" s="1" t="n"/>
-      <c r="GY1" s="1" t="n"/>
-      <c r="GZ1" s="1" t="n"/>
-      <c r="HA1" s="1" t="n"/>
-      <c r="HB1" s="1" t="n"/>
-      <c r="HC1" s="1" t="n"/>
-      <c r="HD1" s="1" t="n"/>
-      <c r="HE1" s="1" t="n"/>
-      <c r="HF1" s="1" t="n"/>
-      <c r="HG1" s="1" t="n"/>
-      <c r="HH1" s="1" t="n"/>
-      <c r="HI1" s="1" t="n"/>
-      <c r="HJ1" s="1" t="n"/>
-      <c r="HK1" s="1" t="n"/>
-      <c r="HL1" s="1" t="n"/>
-      <c r="HM1" s="1" t="n"/>
-      <c r="HN1" s="1" t="n"/>
-      <c r="HO1" s="1" t="n"/>
-      <c r="HP1" s="1" t="n"/>
-      <c r="HQ1" s="1" t="n"/>
-      <c r="HR1" s="1" t="n"/>
-      <c r="HS1" s="1" t="n"/>
-      <c r="HT1" s="1" t="n"/>
-      <c r="HU1" s="1" t="n"/>
-      <c r="HV1" s="1" t="n"/>
-      <c r="HW1" s="1" t="n"/>
-      <c r="HX1" s="1" t="n"/>
-      <c r="HY1" s="1" t="n"/>
-      <c r="HZ1" s="1" t="n"/>
-      <c r="IA1" s="1" t="n"/>
-      <c r="IB1" s="1" t="n"/>
-      <c r="IC1" s="1" t="n"/>
-      <c r="ID1" s="1" t="n"/>
-      <c r="IE1" s="1" t="n"/>
-      <c r="IF1" s="1" t="n"/>
-      <c r="IG1" s="1" t="n"/>
-      <c r="IH1" s="1" t="n"/>
-      <c r="II1" s="1" t="n"/>
-      <c r="IJ1" s="1" t="n"/>
-      <c r="IK1" s="1" t="n"/>
-      <c r="IL1" s="1" t="n"/>
-      <c r="IM1" s="1" t="n"/>
-      <c r="IN1" s="1" t="n"/>
-      <c r="IO1" s="1" t="n"/>
-      <c r="IP1" s="1" t="n"/>
-      <c r="IQ1" s="1" t="n"/>
-      <c r="IR1" s="1" t="n"/>
-      <c r="IS1" s="1" t="n"/>
-      <c r="IT1" s="1" t="n"/>
-      <c r="IU1" s="1" t="n"/>
+      <c r="FK1" s="25" t="n"/>
+      <c r="FL1" s="25" t="n"/>
+      <c r="FM1" s="25" t="n"/>
+      <c r="FN1" s="25" t="n"/>
+      <c r="FO1" s="25" t="n"/>
+      <c r="FP1" s="25" t="n"/>
+      <c r="FQ1" s="25" t="n"/>
+      <c r="FR1" s="25" t="n"/>
+      <c r="FS1" s="25" t="n"/>
+      <c r="FT1" s="25" t="n"/>
+      <c r="FU1" s="25" t="n"/>
+      <c r="FV1" s="25" t="n"/>
+      <c r="FW1" s="25" t="n"/>
+      <c r="FX1" s="25" t="n"/>
+      <c r="FY1" s="25" t="n"/>
+      <c r="FZ1" s="25" t="n"/>
+      <c r="GA1" s="25" t="n"/>
+      <c r="GB1" s="25" t="n"/>
+      <c r="GC1" s="25" t="n"/>
+      <c r="GD1" s="25" t="n"/>
+      <c r="GE1" s="25" t="n"/>
+      <c r="GF1" s="25" t="n"/>
+      <c r="GG1" s="25" t="n"/>
+      <c r="GH1" s="25" t="n"/>
+      <c r="GI1" s="25" t="n"/>
+      <c r="GJ1" s="25" t="n"/>
+      <c r="GK1" s="25" t="n"/>
+      <c r="GL1" s="25" t="n"/>
+      <c r="GM1" s="25" t="n"/>
+      <c r="GN1" s="25" t="n"/>
+      <c r="GO1" s="25" t="n"/>
+      <c r="GP1" s="25" t="n"/>
+      <c r="GQ1" s="25" t="n"/>
+      <c r="GR1" s="25" t="n"/>
+      <c r="GS1" s="25" t="n"/>
+      <c r="GT1" s="25" t="n"/>
+      <c r="GU1" s="25" t="n"/>
+      <c r="GV1" s="25" t="n"/>
+      <c r="GW1" s="25" t="n"/>
+      <c r="GX1" s="25" t="n"/>
+      <c r="GY1" s="25" t="n"/>
+      <c r="GZ1" s="25" t="n"/>
+      <c r="HA1" s="25" t="n"/>
+      <c r="HB1" s="25" t="n"/>
+      <c r="HC1" s="25" t="n"/>
+      <c r="HD1" s="25" t="n"/>
+      <c r="HE1" s="25" t="n"/>
+      <c r="HF1" s="25" t="n"/>
+      <c r="HG1" s="25" t="n"/>
+      <c r="HH1" s="25" t="n"/>
+      <c r="HI1" s="25" t="n"/>
+      <c r="HJ1" s="25" t="n"/>
+      <c r="HK1" s="25" t="n"/>
+      <c r="HL1" s="25" t="n"/>
+      <c r="HM1" s="25" t="n"/>
+      <c r="HN1" s="25" t="n"/>
+      <c r="HO1" s="25" t="n"/>
+      <c r="HP1" s="25" t="n"/>
+      <c r="HQ1" s="25" t="n"/>
+      <c r="HR1" s="25" t="n"/>
+      <c r="HS1" s="25" t="n"/>
+      <c r="HT1" s="25" t="n"/>
+      <c r="HU1" s="25" t="n"/>
+      <c r="HV1" s="25" t="n"/>
+      <c r="HW1" s="25" t="n"/>
+      <c r="HX1" s="25" t="n"/>
+      <c r="HY1" s="25" t="n"/>
+      <c r="HZ1" s="25" t="n"/>
+      <c r="IA1" s="25" t="n"/>
+      <c r="IB1" s="25" t="n"/>
+      <c r="IC1" s="25" t="n"/>
+      <c r="ID1" s="25" t="n"/>
+      <c r="IE1" s="25" t="n"/>
+      <c r="IF1" s="25" t="n"/>
+      <c r="IG1" s="25" t="n"/>
+      <c r="IH1" s="25" t="n"/>
+      <c r="II1" s="25" t="n"/>
+      <c r="IJ1" s="25" t="n"/>
+      <c r="IK1" s="25" t="n"/>
+      <c r="IL1" s="25" t="n"/>
+      <c r="IM1" s="25" t="n"/>
+      <c r="IN1" s="25" t="n"/>
+      <c r="IO1" s="25" t="n"/>
+      <c r="IP1" s="25" t="n"/>
+      <c r="IQ1" s="25" t="n"/>
+      <c r="IR1" s="25" t="n"/>
+      <c r="IS1" s="25" t="n"/>
+      <c r="IT1" s="25" t="n"/>
+      <c r="IU1" s="26" t="n"/>
       <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>SAFETY &amp; ADVERSE EVENTS</t>
         </is>
       </c>
-      <c r="IW1" s="1" t="n"/>
-      <c r="IX1" s="1" t="n"/>
-      <c r="IY1" s="1" t="n"/>
-      <c r="IZ1" s="1" t="n"/>
-      <c r="JA1" s="1" t="n"/>
-      <c r="JB1" s="1" t="n"/>
-      <c r="JC1" s="1" t="n"/>
-      <c r="JD1" s="1" t="n"/>
-      <c r="JE1" s="1" t="n"/>
-      <c r="JF1" s="1" t="n"/>
-      <c r="JG1" s="1" t="n"/>
-      <c r="JH1" s="1" t="n"/>
-      <c r="JI1" s="1" t="n"/>
-      <c r="JJ1" s="1" t="n"/>
-      <c r="JK1" s="1" t="n"/>
-      <c r="JL1" s="1" t="n"/>
-      <c r="JM1" s="1" t="n"/>
-      <c r="JN1" s="1" t="n"/>
-      <c r="JO1" s="1" t="n"/>
-      <c r="JP1" s="1" t="n"/>
-      <c r="JQ1" s="1" t="n"/>
-      <c r="JR1" s="1" t="n"/>
-      <c r="JS1" s="1" t="n"/>
+      <c r="IW1" s="25" t="n"/>
+      <c r="IX1" s="25" t="n"/>
+      <c r="IY1" s="25" t="n"/>
+      <c r="IZ1" s="25" t="n"/>
+      <c r="JA1" s="25" t="n"/>
+      <c r="JB1" s="25" t="n"/>
+      <c r="JC1" s="25" t="n"/>
+      <c r="JD1" s="25" t="n"/>
+      <c r="JE1" s="25" t="n"/>
+      <c r="JF1" s="25" t="n"/>
+      <c r="JG1" s="25" t="n"/>
+      <c r="JH1" s="25" t="n"/>
+      <c r="JI1" s="25" t="n"/>
+      <c r="JJ1" s="25" t="n"/>
+      <c r="JK1" s="25" t="n"/>
+      <c r="JL1" s="25" t="n"/>
+      <c r="JM1" s="25" t="n"/>
+      <c r="JN1" s="25" t="n"/>
+      <c r="JO1" s="25" t="n"/>
+      <c r="JP1" s="25" t="n"/>
+      <c r="JQ1" s="25" t="n"/>
+      <c r="JR1" s="25" t="n"/>
+      <c r="JS1" s="26" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1205,13 +1851,13 @@
           <t>Dose</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="26" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="26" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Study Phase</t>
@@ -1222,7 +1868,7 @@
           <t>Period of Study</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="26" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Total Cohort (N)</t>
@@ -1238,29 +1884,29 @@
           <t>Age</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="N2" s="25" t="n"/>
+      <c r="O2" s="26" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Drug Naive</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
+      <c r="Q2" s="25" t="n"/>
+      <c r="R2" s="26" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Treated</t>
         </is>
       </c>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
+      <c r="T2" s="25" t="n"/>
+      <c r="U2" s="26" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Run In</t>
         </is>
       </c>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
+      <c r="W2" s="25" t="n"/>
+      <c r="X2" s="26" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Type 2 Diabetes Diagnosis</t>
@@ -1341,433 +1987,433 @@
           <t>Male Stratum</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="n"/>
+      <c r="AO2" s="26" t="n"/>
       <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>Female Stratum</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="n"/>
+      <c r="AQ2" s="26" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="n"/>
+      <c r="AS2" s="26" t="n"/>
       <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>sex: male</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="n"/>
-      <c r="AV2" s="2" t="n"/>
-      <c r="AW2" s="2" t="n"/>
-      <c r="AX2" s="2" t="n"/>
+      <c r="AU2" s="25" t="n"/>
+      <c r="AV2" s="25" t="n"/>
+      <c r="AW2" s="25" t="n"/>
+      <c r="AX2" s="26" t="n"/>
       <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="AZ2" s="2" t="n"/>
-      <c r="BA2" s="2" t="n"/>
-      <c r="BB2" s="2" t="n"/>
-      <c r="BC2" s="2" t="n"/>
+      <c r="AZ2" s="25" t="n"/>
+      <c r="BA2" s="25" t="n"/>
+      <c r="BB2" s="25" t="n"/>
+      <c r="BC2" s="26" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>body_weight</t>
         </is>
       </c>
-      <c r="BE2" s="2" t="n"/>
-      <c r="BF2" s="2" t="n"/>
-      <c r="BG2" s="2" t="n"/>
-      <c r="BH2" s="2" t="n"/>
+      <c r="BE2" s="25" t="n"/>
+      <c r="BF2" s="25" t="n"/>
+      <c r="BG2" s="25" t="n"/>
+      <c r="BH2" s="26" t="n"/>
       <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
       </c>
-      <c r="BJ2" s="2" t="n"/>
-      <c r="BK2" s="2" t="n"/>
-      <c r="BL2" s="2" t="n"/>
-      <c r="BM2" s="2" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="25" t="n"/>
+      <c r="BL2" s="25" t="n"/>
+      <c r="BM2" s="26" t="n"/>
       <c r="BN2" s="2" t="inlineStr">
         <is>
           <t>hba1c</t>
         </is>
       </c>
-      <c r="BO2" s="2" t="n"/>
-      <c r="BP2" s="2" t="n"/>
-      <c r="BQ2" s="2" t="n"/>
-      <c r="BR2" s="2" t="n"/>
+      <c r="BO2" s="25" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="25" t="n"/>
+      <c r="BR2" s="26" t="n"/>
       <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>fasting plasma glucose</t>
         </is>
       </c>
-      <c r="BT2" s="2" t="n"/>
-      <c r="BU2" s="2" t="n"/>
-      <c r="BV2" s="2" t="n"/>
-      <c r="BW2" s="2" t="n"/>
+      <c r="BT2" s="25" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="25" t="n"/>
+      <c r="BW2" s="26" t="n"/>
       <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>ppg auc1-4h</t>
         </is>
       </c>
-      <c r="BY2" s="2" t="n"/>
-      <c r="BZ2" s="2" t="n"/>
-      <c r="CA2" s="2" t="n"/>
-      <c r="CB2" s="2" t="n"/>
+      <c r="BY2" s="25" t="n"/>
+      <c r="BZ2" s="25" t="n"/>
+      <c r="CA2" s="25" t="n"/>
+      <c r="CB2" s="26" t="n"/>
       <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>24-hour mean glucose</t>
         </is>
       </c>
-      <c r="CD2" s="2" t="n"/>
-      <c r="CE2" s="2" t="n"/>
-      <c r="CF2" s="2" t="n"/>
-      <c r="CG2" s="2" t="n"/>
+      <c r="CD2" s="25" t="n"/>
+      <c r="CE2" s="25" t="n"/>
+      <c r="CF2" s="25" t="n"/>
+      <c r="CG2" s="26" t="n"/>
       <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="CI2" s="2" t="n"/>
-      <c r="CJ2" s="2" t="n"/>
-      <c r="CK2" s="2" t="n"/>
-      <c r="CL2" s="2" t="n"/>
+      <c r="CI2" s="25" t="n"/>
+      <c r="CJ2" s="25" t="n"/>
+      <c r="CK2" s="25" t="n"/>
+      <c r="CL2" s="26" t="n"/>
       <c r="CM2" s="2" t="inlineStr">
         <is>
           <t>egfr</t>
         </is>
       </c>
-      <c r="CN2" s="2" t="n"/>
-      <c r="CO2" s="2" t="n"/>
-      <c r="CP2" s="2" t="n"/>
-      <c r="CQ2" s="2" t="n"/>
+      <c r="CN2" s="25" t="n"/>
+      <c r="CO2" s="25" t="n"/>
+      <c r="CP2" s="25" t="n"/>
+      <c r="CQ2" s="26" t="n"/>
       <c r="CR2" s="2" t="inlineStr">
         <is>
           <t>systolic blood pressure</t>
         </is>
       </c>
-      <c r="CS2" s="2" t="n"/>
-      <c r="CT2" s="2" t="n"/>
-      <c r="CU2" s="2" t="n"/>
-      <c r="CV2" s="2" t="n"/>
+      <c r="CS2" s="25" t="n"/>
+      <c r="CT2" s="25" t="n"/>
+      <c r="CU2" s="25" t="n"/>
+      <c r="CV2" s="26" t="n"/>
       <c r="CW2" s="2" t="inlineStr">
         <is>
           <t>diastolic blood pressure</t>
         </is>
       </c>
-      <c r="CX2" s="2" t="n"/>
-      <c r="CY2" s="2" t="n"/>
-      <c r="CZ2" s="2" t="n"/>
-      <c r="DA2" s="2" t="n"/>
+      <c r="CX2" s="25" t="n"/>
+      <c r="CY2" s="25" t="n"/>
+      <c r="CZ2" s="25" t="n"/>
+      <c r="DA2" s="26" t="n"/>
       <c r="DB2" s="2" t="inlineStr">
         <is>
           <t>insulin auc1-4h</t>
         </is>
       </c>
-      <c r="DC2" s="2" t="n"/>
-      <c r="DD2" s="2" t="n"/>
-      <c r="DE2" s="2" t="n"/>
-      <c r="DF2" s="2" t="n"/>
+      <c r="DC2" s="25" t="n"/>
+      <c r="DD2" s="25" t="n"/>
+      <c r="DE2" s="25" t="n"/>
+      <c r="DF2" s="26" t="n"/>
       <c r="DG2" s="2" t="inlineStr">
         <is>
           <t>insulin auc10-13h</t>
         </is>
       </c>
-      <c r="DH2" s="2" t="n"/>
-      <c r="DI2" s="2" t="n"/>
-      <c r="DJ2" s="2" t="n"/>
-      <c r="DK2" s="2" t="n"/>
+      <c r="DH2" s="25" t="n"/>
+      <c r="DI2" s="25" t="n"/>
+      <c r="DJ2" s="25" t="n"/>
+      <c r="DK2" s="26" t="n"/>
       <c r="DL2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (fasting)</t>
         </is>
       </c>
-      <c r="DM2" s="2" t="n"/>
-      <c r="DN2" s="2" t="n"/>
-      <c r="DO2" s="2" t="n"/>
-      <c r="DP2" s="2" t="n"/>
+      <c r="DM2" s="25" t="n"/>
+      <c r="DN2" s="25" t="n"/>
+      <c r="DO2" s="25" t="n"/>
+      <c r="DP2" s="26" t="n"/>
       <c r="DQ2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (24h)</t>
         </is>
       </c>
-      <c r="DR2" s="2" t="n"/>
-      <c r="DS2" s="2" t="n"/>
-      <c r="DT2" s="2" t="n"/>
-      <c r="DU2" s="2" t="n"/>
+      <c r="DR2" s="25" t="n"/>
+      <c r="DS2" s="25" t="n"/>
+      <c r="DT2" s="25" t="n"/>
+      <c r="DU2" s="26" t="n"/>
       <c r="DV2" s="2" t="inlineStr">
         <is>
           <t>total_cholesterol</t>
         </is>
       </c>
-      <c r="DW2" s="2" t="n"/>
-      <c r="DX2" s="2" t="n"/>
-      <c r="DY2" s="2" t="n"/>
-      <c r="DZ2" s="2" t="n"/>
+      <c r="DW2" s="25" t="n"/>
+      <c r="DX2" s="25" t="n"/>
+      <c r="DY2" s="25" t="n"/>
+      <c r="DZ2" s="26" t="n"/>
       <c r="EA2" s="2" t="inlineStr">
         <is>
           <t>hdl-c</t>
         </is>
       </c>
-      <c r="EB2" s="2" t="n"/>
-      <c r="EC2" s="2" t="n"/>
-      <c r="ED2" s="2" t="n"/>
-      <c r="EE2" s="2" t="n"/>
+      <c r="EB2" s="25" t="n"/>
+      <c r="EC2" s="25" t="n"/>
+      <c r="ED2" s="25" t="n"/>
+      <c r="EE2" s="26" t="n"/>
       <c r="EF2" s="2" t="inlineStr">
         <is>
           <t>ldl-c</t>
         </is>
       </c>
-      <c r="EG2" s="2" t="n"/>
-      <c r="EH2" s="2" t="n"/>
-      <c r="EI2" s="2" t="n"/>
-      <c r="EJ2" s="2" t="n"/>
+      <c r="EG2" s="25" t="n"/>
+      <c r="EH2" s="25" t="n"/>
+      <c r="EI2" s="25" t="n"/>
+      <c r="EJ2" s="26" t="n"/>
       <c r="EK2" s="2" t="inlineStr">
         <is>
           <t>triglycerides</t>
         </is>
       </c>
-      <c r="EL2" s="2" t="n"/>
-      <c r="EM2" s="2" t="n"/>
-      <c r="EN2" s="2" t="n"/>
-      <c r="EO2" s="2" t="n"/>
+      <c r="EL2" s="25" t="n"/>
+      <c r="EM2" s="25" t="n"/>
+      <c r="EN2" s="25" t="n"/>
+      <c r="EO2" s="26" t="n"/>
       <c r="EP2" s="2" t="inlineStr">
         <is>
           <t>free fatty acids</t>
         </is>
       </c>
-      <c r="EQ2" s="2" t="n"/>
-      <c r="ER2" s="2" t="n"/>
-      <c r="ES2" s="2" t="n"/>
-      <c r="ET2" s="2" t="n"/>
+      <c r="EQ2" s="25" t="n"/>
+      <c r="ER2" s="25" t="n"/>
+      <c r="ES2" s="25" t="n"/>
+      <c r="ET2" s="26" t="n"/>
       <c r="EU2" s="2" t="inlineStr">
         <is>
           <t>total ketone bodies</t>
         </is>
       </c>
-      <c r="EV2" s="2" t="n"/>
-      <c r="EW2" s="2" t="n"/>
-      <c r="EX2" s="2" t="n"/>
-      <c r="EY2" s="2" t="n"/>
+      <c r="EV2" s="25" t="n"/>
+      <c r="EW2" s="25" t="n"/>
+      <c r="EX2" s="25" t="n"/>
+      <c r="EY2" s="26" t="n"/>
       <c r="EZ2" s="2" t="inlineStr">
         <is>
           <t>sex: female</t>
         </is>
       </c>
-      <c r="FA2" s="2" t="n"/>
-      <c r="FB2" s="2" t="n"/>
-      <c r="FC2" s="2" t="n"/>
-      <c r="FD2" s="2" t="n"/>
+      <c r="FA2" s="25" t="n"/>
+      <c r="FB2" s="25" t="n"/>
+      <c r="FC2" s="25" t="n"/>
+      <c r="FD2" s="26" t="n"/>
       <c r="FE2" s="2" t="inlineStr">
         <is>
           <t>race: asian (japanese)</t>
         </is>
       </c>
-      <c r="FF2" s="2" t="n"/>
-      <c r="FG2" s="2" t="n"/>
-      <c r="FH2" s="2" t="n"/>
-      <c r="FI2" s="2" t="n"/>
+      <c r="FF2" s="25" t="n"/>
+      <c r="FG2" s="25" t="n"/>
+      <c r="FH2" s="25" t="n"/>
+      <c r="FI2" s="26" t="n"/>
       <c r="FJ2" s="2" t="inlineStr">
         <is>
           <t>insulin auc1-4h</t>
         </is>
       </c>
-      <c r="FK2" s="2" t="n"/>
-      <c r="FL2" s="2" t="n"/>
-      <c r="FM2" s="2" t="n"/>
-      <c r="FN2" s="2" t="n"/>
-      <c r="FO2" s="2" t="n"/>
+      <c r="FK2" s="25" t="n"/>
+      <c r="FL2" s="25" t="n"/>
+      <c r="FM2" s="25" t="n"/>
+      <c r="FN2" s="25" t="n"/>
+      <c r="FO2" s="26" t="n"/>
       <c r="FP2" s="2" t="inlineStr">
         <is>
           <t>insulin auc10-13h</t>
         </is>
       </c>
-      <c r="FQ2" s="2" t="n"/>
-      <c r="FR2" s="2" t="n"/>
-      <c r="FS2" s="2" t="n"/>
-      <c r="FT2" s="2" t="n"/>
-      <c r="FU2" s="2" t="n"/>
+      <c r="FQ2" s="25" t="n"/>
+      <c r="FR2" s="25" t="n"/>
+      <c r="FS2" s="25" t="n"/>
+      <c r="FT2" s="25" t="n"/>
+      <c r="FU2" s="26" t="n"/>
       <c r="FV2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (fasting)</t>
         </is>
       </c>
-      <c r="FW2" s="2" t="n"/>
-      <c r="FX2" s="2" t="n"/>
-      <c r="FY2" s="2" t="n"/>
-      <c r="FZ2" s="2" t="n"/>
-      <c r="GA2" s="2" t="n"/>
+      <c r="FW2" s="25" t="n"/>
+      <c r="FX2" s="25" t="n"/>
+      <c r="FY2" s="25" t="n"/>
+      <c r="FZ2" s="25" t="n"/>
+      <c r="GA2" s="26" t="n"/>
       <c r="GB2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (24h)</t>
         </is>
       </c>
-      <c r="GC2" s="2" t="n"/>
-      <c r="GD2" s="2" t="n"/>
-      <c r="GE2" s="2" t="n"/>
-      <c r="GF2" s="2" t="n"/>
-      <c r="GG2" s="2" t="n"/>
+      <c r="GC2" s="25" t="n"/>
+      <c r="GD2" s="25" t="n"/>
+      <c r="GE2" s="25" t="n"/>
+      <c r="GF2" s="25" t="n"/>
+      <c r="GG2" s="26" t="n"/>
       <c r="GH2" s="2" t="inlineStr">
         <is>
           <t>total_cholesterol</t>
         </is>
       </c>
-      <c r="GI2" s="2" t="n"/>
-      <c r="GJ2" s="2" t="n"/>
-      <c r="GK2" s="2" t="n"/>
-      <c r="GL2" s="2" t="n"/>
-      <c r="GM2" s="2" t="n"/>
+      <c r="GI2" s="25" t="n"/>
+      <c r="GJ2" s="25" t="n"/>
+      <c r="GK2" s="25" t="n"/>
+      <c r="GL2" s="25" t="n"/>
+      <c r="GM2" s="26" t="n"/>
       <c r="GN2" s="2" t="inlineStr">
         <is>
           <t>hdl-c</t>
         </is>
       </c>
-      <c r="GO2" s="2" t="n"/>
-      <c r="GP2" s="2" t="n"/>
-      <c r="GQ2" s="2" t="n"/>
-      <c r="GR2" s="2" t="n"/>
-      <c r="GS2" s="2" t="n"/>
+      <c r="GO2" s="25" t="n"/>
+      <c r="GP2" s="25" t="n"/>
+      <c r="GQ2" s="25" t="n"/>
+      <c r="GR2" s="25" t="n"/>
+      <c r="GS2" s="26" t="n"/>
       <c r="GT2" s="2" t="inlineStr">
         <is>
           <t>ldl-c</t>
         </is>
       </c>
-      <c r="GU2" s="2" t="n"/>
-      <c r="GV2" s="2" t="n"/>
-      <c r="GW2" s="2" t="n"/>
-      <c r="GX2" s="2" t="n"/>
-      <c r="GY2" s="2" t="n"/>
+      <c r="GU2" s="25" t="n"/>
+      <c r="GV2" s="25" t="n"/>
+      <c r="GW2" s="25" t="n"/>
+      <c r="GX2" s="25" t="n"/>
+      <c r="GY2" s="26" t="n"/>
       <c r="GZ2" s="2" t="inlineStr">
         <is>
           <t>triglycerides</t>
         </is>
       </c>
-      <c r="HA2" s="2" t="n"/>
-      <c r="HB2" s="2" t="n"/>
-      <c r="HC2" s="2" t="n"/>
-      <c r="HD2" s="2" t="n"/>
-      <c r="HE2" s="2" t="n"/>
+      <c r="HA2" s="25" t="n"/>
+      <c r="HB2" s="25" t="n"/>
+      <c r="HC2" s="25" t="n"/>
+      <c r="HD2" s="25" t="n"/>
+      <c r="HE2" s="26" t="n"/>
       <c r="HF2" s="2" t="inlineStr">
         <is>
           <t>free fatty acids</t>
         </is>
       </c>
-      <c r="HG2" s="2" t="n"/>
-      <c r="HH2" s="2" t="n"/>
-      <c r="HI2" s="2" t="n"/>
-      <c r="HJ2" s="2" t="n"/>
-      <c r="HK2" s="2" t="n"/>
+      <c r="HG2" s="25" t="n"/>
+      <c r="HH2" s="25" t="n"/>
+      <c r="HI2" s="25" t="n"/>
+      <c r="HJ2" s="25" t="n"/>
+      <c r="HK2" s="26" t="n"/>
       <c r="HL2" s="2" t="inlineStr">
         <is>
           <t>total ketone bodies</t>
         </is>
       </c>
-      <c r="HM2" s="2" t="n"/>
-      <c r="HN2" s="2" t="n"/>
-      <c r="HO2" s="2" t="n"/>
-      <c r="HP2" s="2" t="n"/>
-      <c r="HQ2" s="2" t="n"/>
+      <c r="HM2" s="25" t="n"/>
+      <c r="HN2" s="25" t="n"/>
+      <c r="HO2" s="25" t="n"/>
+      <c r="HP2" s="25" t="n"/>
+      <c r="HQ2" s="26" t="n"/>
       <c r="HR2" s="2" t="inlineStr">
         <is>
           <t>ppg auc1-4h</t>
         </is>
       </c>
-      <c r="HS2" s="2" t="n"/>
-      <c r="HT2" s="2" t="n"/>
-      <c r="HU2" s="2" t="n"/>
-      <c r="HV2" s="2" t="n"/>
-      <c r="HW2" s="2" t="n"/>
+      <c r="HS2" s="25" t="n"/>
+      <c r="HT2" s="25" t="n"/>
+      <c r="HU2" s="25" t="n"/>
+      <c r="HV2" s="25" t="n"/>
+      <c r="HW2" s="26" t="n"/>
       <c r="HX2" s="2" t="inlineStr">
         <is>
           <t>fasting plasma glucose</t>
         </is>
       </c>
-      <c r="HY2" s="2" t="n"/>
-      <c r="HZ2" s="2" t="n"/>
-      <c r="IA2" s="2" t="n"/>
-      <c r="IB2" s="2" t="n"/>
-      <c r="IC2" s="2" t="n"/>
+      <c r="HY2" s="25" t="n"/>
+      <c r="HZ2" s="25" t="n"/>
+      <c r="IA2" s="25" t="n"/>
+      <c r="IB2" s="25" t="n"/>
+      <c r="IC2" s="26" t="n"/>
       <c r="ID2" s="2" t="inlineStr">
         <is>
           <t>24-hour mean glucose</t>
         </is>
       </c>
-      <c r="IE2" s="2" t="n"/>
-      <c r="IF2" s="2" t="n"/>
-      <c r="IG2" s="2" t="n"/>
-      <c r="IH2" s="2" t="n"/>
-      <c r="II2" s="2" t="n"/>
+      <c r="IE2" s="25" t="n"/>
+      <c r="IF2" s="25" t="n"/>
+      <c r="IG2" s="25" t="n"/>
+      <c r="IH2" s="25" t="n"/>
+      <c r="II2" s="26" t="n"/>
       <c r="IJ2" s="2" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="IK2" s="2" t="n"/>
-      <c r="IL2" s="2" t="n"/>
-      <c r="IM2" s="2" t="n"/>
-      <c r="IN2" s="2" t="n"/>
-      <c r="IO2" s="2" t="n"/>
+      <c r="IK2" s="25" t="n"/>
+      <c r="IL2" s="25" t="n"/>
+      <c r="IM2" s="25" t="n"/>
+      <c r="IN2" s="25" t="n"/>
+      <c r="IO2" s="26" t="n"/>
       <c r="IP2" s="2" t="inlineStr">
         <is>
           <t>hba1c</t>
         </is>
       </c>
-      <c r="IQ2" s="2" t="n"/>
-      <c r="IR2" s="2" t="n"/>
-      <c r="IS2" s="2" t="n"/>
-      <c r="IT2" s="2" t="n"/>
-      <c r="IU2" s="2" t="n"/>
+      <c r="IQ2" s="25" t="n"/>
+      <c r="IR2" s="25" t="n"/>
+      <c r="IS2" s="25" t="n"/>
+      <c r="IT2" s="25" t="n"/>
+      <c r="IU2" s="26" t="n"/>
       <c r="IV2" s="2" t="inlineStr">
         <is>
           <t>any adverse event</t>
         </is>
       </c>
-      <c r="IW2" s="2" t="n"/>
-      <c r="IX2" s="2" t="n"/>
-      <c r="IY2" s="2" t="n"/>
+      <c r="IW2" s="25" t="n"/>
+      <c r="IX2" s="25" t="n"/>
+      <c r="IY2" s="26" t="n"/>
       <c r="IZ2" s="2" t="inlineStr">
         <is>
           <t>severe adverse events</t>
         </is>
       </c>
-      <c r="JA2" s="2" t="n"/>
-      <c r="JB2" s="2" t="n"/>
-      <c r="JC2" s="2" t="n"/>
+      <c r="JA2" s="25" t="n"/>
+      <c r="JB2" s="25" t="n"/>
+      <c r="JC2" s="26" t="n"/>
       <c r="JD2" s="2" t="inlineStr">
         <is>
           <t>serious adverse events</t>
         </is>
       </c>
-      <c r="JE2" s="2" t="n"/>
-      <c r="JF2" s="2" t="n"/>
-      <c r="JG2" s="2" t="n"/>
+      <c r="JE2" s="25" t="n"/>
+      <c r="JF2" s="25" t="n"/>
+      <c r="JG2" s="26" t="n"/>
       <c r="JH2" s="2" t="inlineStr">
         <is>
           <t>discontinuation due to adverse events</t>
         </is>
       </c>
-      <c r="JI2" s="2" t="n"/>
-      <c r="JJ2" s="2" t="n"/>
-      <c r="JK2" s="2" t="n"/>
+      <c r="JI2" s="25" t="n"/>
+      <c r="JJ2" s="25" t="n"/>
+      <c r="JK2" s="26" t="n"/>
       <c r="JL2" s="2" t="inlineStr">
         <is>
           <t>hypoglycemia</t>
         </is>
       </c>
-      <c r="JM2" s="2" t="n"/>
-      <c r="JN2" s="2" t="n"/>
-      <c r="JO2" s="2" t="n"/>
+      <c r="JM2" s="25" t="n"/>
+      <c r="JN2" s="25" t="n"/>
+      <c r="JO2" s="26" t="n"/>
       <c r="JP2" s="2" t="inlineStr">
         <is>
           <t>genital infection</t>
         </is>
       </c>
-      <c r="JQ2" s="2" t="n"/>
-      <c r="JR2" s="2" t="n"/>
-      <c r="JS2" s="2" t="n"/>
+      <c r="JQ2" s="25" t="n"/>
+      <c r="JR2" s="25" t="n"/>
+      <c r="JS2" s="26" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
@@ -11504,6 +12150,7 @@
     <mergeCell ref="S2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11542,7 +12189,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -14849,6 +15495,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14988,6 +15635,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25318,6 +25966,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28444,6 +29093,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28484,7 +29134,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -29749,6 +30398,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29791,7 +30441,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -32895,8 +33544,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
@@ -34118,6 +34765,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34155,7 +34803,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -42837,6 +43484,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -42876,7 +43524,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -42908,7 +43555,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
@@ -42960,7 +43606,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
@@ -43016,7 +43661,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -43070,6 +43714,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -43111,7 +43756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -43491,7 +44135,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -43548,7 +44191,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -43620,7 +44262,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
@@ -43704,6 +44345,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -43737,7 +44379,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -43799,8 +44440,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
@@ -43918,6 +44557,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44064,6 +44704,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44193,7 +44834,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -44411,6 +45051,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44657,6 +45298,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45650,6 +46292,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -63285,6 +63928,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -63471,6 +64115,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -63579,6 +64224,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -63621,7 +64267,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -66936,6 +67581,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -66977,7 +67623,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -70017,5 +70662,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/outputs/Custom_Drug_MANDOROS_Master_Report_CORRECTED.xlsx
+++ b/outputs/Custom_Drug_MANDOROS_Master_Report_CORRECTED.xlsx
@@ -146,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -168,55 +168,11 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -270,8 +226,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -357,7 +311,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="476250" cy="476250"/>
+    <ext cx="523875" cy="523875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -772,7 +726,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>18</col>
+      <col>21</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -802,7 +756,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>40</col>
+      <col>46</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -1527,308 +1481,308 @@
           <t>STUDY &amp; INTERVENTION ARMS</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="25" t="n"/>
-      <c r="J1" s="25" t="n"/>
-      <c r="K1" s="25" t="n"/>
-      <c r="L1" s="26" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>INCLUSION CRITERIA</t>
         </is>
       </c>
-      <c r="N1" s="25" t="n"/>
-      <c r="O1" s="25" t="n"/>
-      <c r="P1" s="25" t="n"/>
-      <c r="Q1" s="25" t="n"/>
-      <c r="R1" s="25" t="n"/>
-      <c r="S1" s="25" t="n"/>
-      <c r="T1" s="25" t="n"/>
-      <c r="U1" s="25" t="n"/>
-      <c r="V1" s="25" t="n"/>
-      <c r="W1" s="25" t="n"/>
-      <c r="X1" s="25" t="n"/>
-      <c r="Y1" s="25" t="n"/>
-      <c r="Z1" s="26" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>EXCLUSION CRITERIA</t>
         </is>
       </c>
-      <c r="AB1" s="25" t="n"/>
-      <c r="AC1" s="25" t="n"/>
-      <c r="AD1" s="25" t="n"/>
-      <c r="AE1" s="25" t="n"/>
-      <c r="AF1" s="25" t="n"/>
-      <c r="AG1" s="25" t="n"/>
-      <c r="AH1" s="25" t="n"/>
-      <c r="AI1" s="25" t="n"/>
-      <c r="AJ1" s="25" t="n"/>
-      <c r="AK1" s="26" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="n"/>
+      <c r="AF1" s="1" t="n"/>
+      <c r="AG1" s="1" t="n"/>
+      <c r="AH1" s="1" t="n"/>
+      <c r="AI1" s="1" t="n"/>
+      <c r="AJ1" s="1" t="n"/>
+      <c r="AK1" s="1" t="n"/>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>POPULATION STRATIFICATION</t>
         </is>
       </c>
-      <c r="AM1" s="25" t="n"/>
-      <c r="AN1" s="25" t="n"/>
-      <c r="AO1" s="25" t="n"/>
-      <c r="AP1" s="25" t="n"/>
-      <c r="AQ1" s="25" t="n"/>
-      <c r="AR1" s="25" t="n"/>
-      <c r="AS1" s="26" t="n"/>
+      <c r="AM1" s="1" t="n"/>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="n"/>
+      <c r="AP1" s="1" t="n"/>
+      <c r="AQ1" s="1" t="n"/>
+      <c r="AR1" s="1" t="n"/>
+      <c r="AS1" s="1" t="n"/>
       <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>BASELINE CHARACTERISTICS &amp; LABS (TIME 0)</t>
         </is>
       </c>
-      <c r="AU1" s="25" t="n"/>
-      <c r="AV1" s="25" t="n"/>
-      <c r="AW1" s="25" t="n"/>
-      <c r="AX1" s="25" t="n"/>
-      <c r="AY1" s="25" t="n"/>
-      <c r="AZ1" s="25" t="n"/>
-      <c r="BA1" s="25" t="n"/>
-      <c r="BB1" s="25" t="n"/>
-      <c r="BC1" s="25" t="n"/>
-      <c r="BD1" s="25" t="n"/>
-      <c r="BE1" s="25" t="n"/>
-      <c r="BF1" s="25" t="n"/>
-      <c r="BG1" s="25" t="n"/>
-      <c r="BH1" s="25" t="n"/>
-      <c r="BI1" s="25" t="n"/>
-      <c r="BJ1" s="25" t="n"/>
-      <c r="BK1" s="25" t="n"/>
-      <c r="BL1" s="25" t="n"/>
-      <c r="BM1" s="25" t="n"/>
-      <c r="BN1" s="25" t="n"/>
-      <c r="BO1" s="25" t="n"/>
-      <c r="BP1" s="25" t="n"/>
-      <c r="BQ1" s="25" t="n"/>
-      <c r="BR1" s="25" t="n"/>
-      <c r="BS1" s="25" t="n"/>
-      <c r="BT1" s="25" t="n"/>
-      <c r="BU1" s="25" t="n"/>
-      <c r="BV1" s="25" t="n"/>
-      <c r="BW1" s="25" t="n"/>
-      <c r="BX1" s="25" t="n"/>
-      <c r="BY1" s="25" t="n"/>
-      <c r="BZ1" s="25" t="n"/>
-      <c r="CA1" s="25" t="n"/>
-      <c r="CB1" s="25" t="n"/>
-      <c r="CC1" s="25" t="n"/>
-      <c r="CD1" s="25" t="n"/>
-      <c r="CE1" s="25" t="n"/>
-      <c r="CF1" s="25" t="n"/>
-      <c r="CG1" s="25" t="n"/>
-      <c r="CH1" s="25" t="n"/>
-      <c r="CI1" s="25" t="n"/>
-      <c r="CJ1" s="25" t="n"/>
-      <c r="CK1" s="25" t="n"/>
-      <c r="CL1" s="25" t="n"/>
-      <c r="CM1" s="25" t="n"/>
-      <c r="CN1" s="25" t="n"/>
-      <c r="CO1" s="25" t="n"/>
-      <c r="CP1" s="25" t="n"/>
-      <c r="CQ1" s="25" t="n"/>
-      <c r="CR1" s="25" t="n"/>
-      <c r="CS1" s="25" t="n"/>
-      <c r="CT1" s="25" t="n"/>
-      <c r="CU1" s="25" t="n"/>
-      <c r="CV1" s="25" t="n"/>
-      <c r="CW1" s="25" t="n"/>
-      <c r="CX1" s="25" t="n"/>
-      <c r="CY1" s="25" t="n"/>
-      <c r="CZ1" s="25" t="n"/>
-      <c r="DA1" s="25" t="n"/>
-      <c r="DB1" s="25" t="n"/>
-      <c r="DC1" s="25" t="n"/>
-      <c r="DD1" s="25" t="n"/>
-      <c r="DE1" s="25" t="n"/>
-      <c r="DF1" s="25" t="n"/>
-      <c r="DG1" s="25" t="n"/>
-      <c r="DH1" s="25" t="n"/>
-      <c r="DI1" s="25" t="n"/>
-      <c r="DJ1" s="25" t="n"/>
-      <c r="DK1" s="25" t="n"/>
-      <c r="DL1" s="25" t="n"/>
-      <c r="DM1" s="25" t="n"/>
-      <c r="DN1" s="25" t="n"/>
-      <c r="DO1" s="25" t="n"/>
-      <c r="DP1" s="25" t="n"/>
-      <c r="DQ1" s="25" t="n"/>
-      <c r="DR1" s="25" t="n"/>
-      <c r="DS1" s="25" t="n"/>
-      <c r="DT1" s="25" t="n"/>
-      <c r="DU1" s="25" t="n"/>
-      <c r="DV1" s="25" t="n"/>
-      <c r="DW1" s="25" t="n"/>
-      <c r="DX1" s="25" t="n"/>
-      <c r="DY1" s="25" t="n"/>
-      <c r="DZ1" s="25" t="n"/>
-      <c r="EA1" s="25" t="n"/>
-      <c r="EB1" s="25" t="n"/>
-      <c r="EC1" s="25" t="n"/>
-      <c r="ED1" s="25" t="n"/>
-      <c r="EE1" s="25" t="n"/>
-      <c r="EF1" s="25" t="n"/>
-      <c r="EG1" s="25" t="n"/>
-      <c r="EH1" s="25" t="n"/>
-      <c r="EI1" s="25" t="n"/>
-      <c r="EJ1" s="25" t="n"/>
-      <c r="EK1" s="25" t="n"/>
-      <c r="EL1" s="25" t="n"/>
-      <c r="EM1" s="25" t="n"/>
-      <c r="EN1" s="25" t="n"/>
-      <c r="EO1" s="25" t="n"/>
-      <c r="EP1" s="25" t="n"/>
-      <c r="EQ1" s="25" t="n"/>
-      <c r="ER1" s="25" t="n"/>
-      <c r="ES1" s="25" t="n"/>
-      <c r="ET1" s="25" t="n"/>
-      <c r="EU1" s="25" t="n"/>
-      <c r="EV1" s="25" t="n"/>
-      <c r="EW1" s="25" t="n"/>
-      <c r="EX1" s="25" t="n"/>
-      <c r="EY1" s="25" t="n"/>
-      <c r="EZ1" s="25" t="n"/>
-      <c r="FA1" s="25" t="n"/>
-      <c r="FB1" s="25" t="n"/>
-      <c r="FC1" s="25" t="n"/>
-      <c r="FD1" s="25" t="n"/>
-      <c r="FE1" s="25" t="n"/>
-      <c r="FF1" s="25" t="n"/>
-      <c r="FG1" s="25" t="n"/>
-      <c r="FH1" s="25" t="n"/>
-      <c r="FI1" s="26" t="n"/>
+      <c r="AU1" s="1" t="n"/>
+      <c r="AV1" s="1" t="n"/>
+      <c r="AW1" s="1" t="n"/>
+      <c r="AX1" s="1" t="n"/>
+      <c r="AY1" s="1" t="n"/>
+      <c r="AZ1" s="1" t="n"/>
+      <c r="BA1" s="1" t="n"/>
+      <c r="BB1" s="1" t="n"/>
+      <c r="BC1" s="1" t="n"/>
+      <c r="BD1" s="1" t="n"/>
+      <c r="BE1" s="1" t="n"/>
+      <c r="BF1" s="1" t="n"/>
+      <c r="BG1" s="1" t="n"/>
+      <c r="BH1" s="1" t="n"/>
+      <c r="BI1" s="1" t="n"/>
+      <c r="BJ1" s="1" t="n"/>
+      <c r="BK1" s="1" t="n"/>
+      <c r="BL1" s="1" t="n"/>
+      <c r="BM1" s="1" t="n"/>
+      <c r="BN1" s="1" t="n"/>
+      <c r="BO1" s="1" t="n"/>
+      <c r="BP1" s="1" t="n"/>
+      <c r="BQ1" s="1" t="n"/>
+      <c r="BR1" s="1" t="n"/>
+      <c r="BS1" s="1" t="n"/>
+      <c r="BT1" s="1" t="n"/>
+      <c r="BU1" s="1" t="n"/>
+      <c r="BV1" s="1" t="n"/>
+      <c r="BW1" s="1" t="n"/>
+      <c r="BX1" s="1" t="n"/>
+      <c r="BY1" s="1" t="n"/>
+      <c r="BZ1" s="1" t="n"/>
+      <c r="CA1" s="1" t="n"/>
+      <c r="CB1" s="1" t="n"/>
+      <c r="CC1" s="1" t="n"/>
+      <c r="CD1" s="1" t="n"/>
+      <c r="CE1" s="1" t="n"/>
+      <c r="CF1" s="1" t="n"/>
+      <c r="CG1" s="1" t="n"/>
+      <c r="CH1" s="1" t="n"/>
+      <c r="CI1" s="1" t="n"/>
+      <c r="CJ1" s="1" t="n"/>
+      <c r="CK1" s="1" t="n"/>
+      <c r="CL1" s="1" t="n"/>
+      <c r="CM1" s="1" t="n"/>
+      <c r="CN1" s="1" t="n"/>
+      <c r="CO1" s="1" t="n"/>
+      <c r="CP1" s="1" t="n"/>
+      <c r="CQ1" s="1" t="n"/>
+      <c r="CR1" s="1" t="n"/>
+      <c r="CS1" s="1" t="n"/>
+      <c r="CT1" s="1" t="n"/>
+      <c r="CU1" s="1" t="n"/>
+      <c r="CV1" s="1" t="n"/>
+      <c r="CW1" s="1" t="n"/>
+      <c r="CX1" s="1" t="n"/>
+      <c r="CY1" s="1" t="n"/>
+      <c r="CZ1" s="1" t="n"/>
+      <c r="DA1" s="1" t="n"/>
+      <c r="DB1" s="1" t="n"/>
+      <c r="DC1" s="1" t="n"/>
+      <c r="DD1" s="1" t="n"/>
+      <c r="DE1" s="1" t="n"/>
+      <c r="DF1" s="1" t="n"/>
+      <c r="DG1" s="1" t="n"/>
+      <c r="DH1" s="1" t="n"/>
+      <c r="DI1" s="1" t="n"/>
+      <c r="DJ1" s="1" t="n"/>
+      <c r="DK1" s="1" t="n"/>
+      <c r="DL1" s="1" t="n"/>
+      <c r="DM1" s="1" t="n"/>
+      <c r="DN1" s="1" t="n"/>
+      <c r="DO1" s="1" t="n"/>
+      <c r="DP1" s="1" t="n"/>
+      <c r="DQ1" s="1" t="n"/>
+      <c r="DR1" s="1" t="n"/>
+      <c r="DS1" s="1" t="n"/>
+      <c r="DT1" s="1" t="n"/>
+      <c r="DU1" s="1" t="n"/>
+      <c r="DV1" s="1" t="n"/>
+      <c r="DW1" s="1" t="n"/>
+      <c r="DX1" s="1" t="n"/>
+      <c r="DY1" s="1" t="n"/>
+      <c r="DZ1" s="1" t="n"/>
+      <c r="EA1" s="1" t="n"/>
+      <c r="EB1" s="1" t="n"/>
+      <c r="EC1" s="1" t="n"/>
+      <c r="ED1" s="1" t="n"/>
+      <c r="EE1" s="1" t="n"/>
+      <c r="EF1" s="1" t="n"/>
+      <c r="EG1" s="1" t="n"/>
+      <c r="EH1" s="1" t="n"/>
+      <c r="EI1" s="1" t="n"/>
+      <c r="EJ1" s="1" t="n"/>
+      <c r="EK1" s="1" t="n"/>
+      <c r="EL1" s="1" t="n"/>
+      <c r="EM1" s="1" t="n"/>
+      <c r="EN1" s="1" t="n"/>
+      <c r="EO1" s="1" t="n"/>
+      <c r="EP1" s="1" t="n"/>
+      <c r="EQ1" s="1" t="n"/>
+      <c r="ER1" s="1" t="n"/>
+      <c r="ES1" s="1" t="n"/>
+      <c r="ET1" s="1" t="n"/>
+      <c r="EU1" s="1" t="n"/>
+      <c r="EV1" s="1" t="n"/>
+      <c r="EW1" s="1" t="n"/>
+      <c r="EX1" s="1" t="n"/>
+      <c r="EY1" s="1" t="n"/>
+      <c r="EZ1" s="1" t="n"/>
+      <c r="FA1" s="1" t="n"/>
+      <c r="FB1" s="1" t="n"/>
+      <c r="FC1" s="1" t="n"/>
+      <c r="FD1" s="1" t="n"/>
+      <c r="FE1" s="1" t="n"/>
+      <c r="FF1" s="1" t="n"/>
+      <c r="FG1" s="1" t="n"/>
+      <c r="FH1" s="1" t="n"/>
+      <c r="FI1" s="1" t="n"/>
       <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>LONGITUDINAL EFFICACY &amp; ENDPOINTS (FOLLOW-UP)</t>
         </is>
       </c>
-      <c r="FK1" s="25" t="n"/>
-      <c r="FL1" s="25" t="n"/>
-      <c r="FM1" s="25" t="n"/>
-      <c r="FN1" s="25" t="n"/>
-      <c r="FO1" s="25" t="n"/>
-      <c r="FP1" s="25" t="n"/>
-      <c r="FQ1" s="25" t="n"/>
-      <c r="FR1" s="25" t="n"/>
-      <c r="FS1" s="25" t="n"/>
-      <c r="FT1" s="25" t="n"/>
-      <c r="FU1" s="25" t="n"/>
-      <c r="FV1" s="25" t="n"/>
-      <c r="FW1" s="25" t="n"/>
-      <c r="FX1" s="25" t="n"/>
-      <c r="FY1" s="25" t="n"/>
-      <c r="FZ1" s="25" t="n"/>
-      <c r="GA1" s="25" t="n"/>
-      <c r="GB1" s="25" t="n"/>
-      <c r="GC1" s="25" t="n"/>
-      <c r="GD1" s="25" t="n"/>
-      <c r="GE1" s="25" t="n"/>
-      <c r="GF1" s="25" t="n"/>
-      <c r="GG1" s="25" t="n"/>
-      <c r="GH1" s="25" t="n"/>
-      <c r="GI1" s="25" t="n"/>
-      <c r="GJ1" s="25" t="n"/>
-      <c r="GK1" s="25" t="n"/>
-      <c r="GL1" s="25" t="n"/>
-      <c r="GM1" s="25" t="n"/>
-      <c r="GN1" s="25" t="n"/>
-      <c r="GO1" s="25" t="n"/>
-      <c r="GP1" s="25" t="n"/>
-      <c r="GQ1" s="25" t="n"/>
-      <c r="GR1" s="25" t="n"/>
-      <c r="GS1" s="25" t="n"/>
-      <c r="GT1" s="25" t="n"/>
-      <c r="GU1" s="25" t="n"/>
-      <c r="GV1" s="25" t="n"/>
-      <c r="GW1" s="25" t="n"/>
-      <c r="GX1" s="25" t="n"/>
-      <c r="GY1" s="25" t="n"/>
-      <c r="GZ1" s="25" t="n"/>
-      <c r="HA1" s="25" t="n"/>
-      <c r="HB1" s="25" t="n"/>
-      <c r="HC1" s="25" t="n"/>
-      <c r="HD1" s="25" t="n"/>
-      <c r="HE1" s="25" t="n"/>
-      <c r="HF1" s="25" t="n"/>
-      <c r="HG1" s="25" t="n"/>
-      <c r="HH1" s="25" t="n"/>
-      <c r="HI1" s="25" t="n"/>
-      <c r="HJ1" s="25" t="n"/>
-      <c r="HK1" s="25" t="n"/>
-      <c r="HL1" s="25" t="n"/>
-      <c r="HM1" s="25" t="n"/>
-      <c r="HN1" s="25" t="n"/>
-      <c r="HO1" s="25" t="n"/>
-      <c r="HP1" s="25" t="n"/>
-      <c r="HQ1" s="25" t="n"/>
-      <c r="HR1" s="25" t="n"/>
-      <c r="HS1" s="25" t="n"/>
-      <c r="HT1" s="25" t="n"/>
-      <c r="HU1" s="25" t="n"/>
-      <c r="HV1" s="25" t="n"/>
-      <c r="HW1" s="25" t="n"/>
-      <c r="HX1" s="25" t="n"/>
-      <c r="HY1" s="25" t="n"/>
-      <c r="HZ1" s="25" t="n"/>
-      <c r="IA1" s="25" t="n"/>
-      <c r="IB1" s="25" t="n"/>
-      <c r="IC1" s="25" t="n"/>
-      <c r="ID1" s="25" t="n"/>
-      <c r="IE1" s="25" t="n"/>
-      <c r="IF1" s="25" t="n"/>
-      <c r="IG1" s="25" t="n"/>
-      <c r="IH1" s="25" t="n"/>
-      <c r="II1" s="25" t="n"/>
-      <c r="IJ1" s="25" t="n"/>
-      <c r="IK1" s="25" t="n"/>
-      <c r="IL1" s="25" t="n"/>
-      <c r="IM1" s="25" t="n"/>
-      <c r="IN1" s="25" t="n"/>
-      <c r="IO1" s="25" t="n"/>
-      <c r="IP1" s="25" t="n"/>
-      <c r="IQ1" s="25" t="n"/>
-      <c r="IR1" s="25" t="n"/>
-      <c r="IS1" s="25" t="n"/>
-      <c r="IT1" s="25" t="n"/>
-      <c r="IU1" s="26" t="n"/>
+      <c r="FK1" s="1" t="n"/>
+      <c r="FL1" s="1" t="n"/>
+      <c r="FM1" s="1" t="n"/>
+      <c r="FN1" s="1" t="n"/>
+      <c r="FO1" s="1" t="n"/>
+      <c r="FP1" s="1" t="n"/>
+      <c r="FQ1" s="1" t="n"/>
+      <c r="FR1" s="1" t="n"/>
+      <c r="FS1" s="1" t="n"/>
+      <c r="FT1" s="1" t="n"/>
+      <c r="FU1" s="1" t="n"/>
+      <c r="FV1" s="1" t="n"/>
+      <c r="FW1" s="1" t="n"/>
+      <c r="FX1" s="1" t="n"/>
+      <c r="FY1" s="1" t="n"/>
+      <c r="FZ1" s="1" t="n"/>
+      <c r="GA1" s="1" t="n"/>
+      <c r="GB1" s="1" t="n"/>
+      <c r="GC1" s="1" t="n"/>
+      <c r="GD1" s="1" t="n"/>
+      <c r="GE1" s="1" t="n"/>
+      <c r="GF1" s="1" t="n"/>
+      <c r="GG1" s="1" t="n"/>
+      <c r="GH1" s="1" t="n"/>
+      <c r="GI1" s="1" t="n"/>
+      <c r="GJ1" s="1" t="n"/>
+      <c r="GK1" s="1" t="n"/>
+      <c r="GL1" s="1" t="n"/>
+      <c r="GM1" s="1" t="n"/>
+      <c r="GN1" s="1" t="n"/>
+      <c r="GO1" s="1" t="n"/>
+      <c r="GP1" s="1" t="n"/>
+      <c r="GQ1" s="1" t="n"/>
+      <c r="GR1" s="1" t="n"/>
+      <c r="GS1" s="1" t="n"/>
+      <c r="GT1" s="1" t="n"/>
+      <c r="GU1" s="1" t="n"/>
+      <c r="GV1" s="1" t="n"/>
+      <c r="GW1" s="1" t="n"/>
+      <c r="GX1" s="1" t="n"/>
+      <c r="GY1" s="1" t="n"/>
+      <c r="GZ1" s="1" t="n"/>
+      <c r="HA1" s="1" t="n"/>
+      <c r="HB1" s="1" t="n"/>
+      <c r="HC1" s="1" t="n"/>
+      <c r="HD1" s="1" t="n"/>
+      <c r="HE1" s="1" t="n"/>
+      <c r="HF1" s="1" t="n"/>
+      <c r="HG1" s="1" t="n"/>
+      <c r="HH1" s="1" t="n"/>
+      <c r="HI1" s="1" t="n"/>
+      <c r="HJ1" s="1" t="n"/>
+      <c r="HK1" s="1" t="n"/>
+      <c r="HL1" s="1" t="n"/>
+      <c r="HM1" s="1" t="n"/>
+      <c r="HN1" s="1" t="n"/>
+      <c r="HO1" s="1" t="n"/>
+      <c r="HP1" s="1" t="n"/>
+      <c r="HQ1" s="1" t="n"/>
+      <c r="HR1" s="1" t="n"/>
+      <c r="HS1" s="1" t="n"/>
+      <c r="HT1" s="1" t="n"/>
+      <c r="HU1" s="1" t="n"/>
+      <c r="HV1" s="1" t="n"/>
+      <c r="HW1" s="1" t="n"/>
+      <c r="HX1" s="1" t="n"/>
+      <c r="HY1" s="1" t="n"/>
+      <c r="HZ1" s="1" t="n"/>
+      <c r="IA1" s="1" t="n"/>
+      <c r="IB1" s="1" t="n"/>
+      <c r="IC1" s="1" t="n"/>
+      <c r="ID1" s="1" t="n"/>
+      <c r="IE1" s="1" t="n"/>
+      <c r="IF1" s="1" t="n"/>
+      <c r="IG1" s="1" t="n"/>
+      <c r="IH1" s="1" t="n"/>
+      <c r="II1" s="1" t="n"/>
+      <c r="IJ1" s="1" t="n"/>
+      <c r="IK1" s="1" t="n"/>
+      <c r="IL1" s="1" t="n"/>
+      <c r="IM1" s="1" t="n"/>
+      <c r="IN1" s="1" t="n"/>
+      <c r="IO1" s="1" t="n"/>
+      <c r="IP1" s="1" t="n"/>
+      <c r="IQ1" s="1" t="n"/>
+      <c r="IR1" s="1" t="n"/>
+      <c r="IS1" s="1" t="n"/>
+      <c r="IT1" s="1" t="n"/>
+      <c r="IU1" s="1" t="n"/>
       <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>SAFETY &amp; ADVERSE EVENTS</t>
         </is>
       </c>
-      <c r="IW1" s="25" t="n"/>
-      <c r="IX1" s="25" t="n"/>
-      <c r="IY1" s="25" t="n"/>
-      <c r="IZ1" s="25" t="n"/>
-      <c r="JA1" s="25" t="n"/>
-      <c r="JB1" s="25" t="n"/>
-      <c r="JC1" s="25" t="n"/>
-      <c r="JD1" s="25" t="n"/>
-      <c r="JE1" s="25" t="n"/>
-      <c r="JF1" s="25" t="n"/>
-      <c r="JG1" s="25" t="n"/>
-      <c r="JH1" s="25" t="n"/>
-      <c r="JI1" s="25" t="n"/>
-      <c r="JJ1" s="25" t="n"/>
-      <c r="JK1" s="25" t="n"/>
-      <c r="JL1" s="25" t="n"/>
-      <c r="JM1" s="25" t="n"/>
-      <c r="JN1" s="25" t="n"/>
-      <c r="JO1" s="25" t="n"/>
-      <c r="JP1" s="25" t="n"/>
-      <c r="JQ1" s="25" t="n"/>
-      <c r="JR1" s="25" t="n"/>
-      <c r="JS1" s="26" t="n"/>
+      <c r="IW1" s="1" t="n"/>
+      <c r="IX1" s="1" t="n"/>
+      <c r="IY1" s="1" t="n"/>
+      <c r="IZ1" s="1" t="n"/>
+      <c r="JA1" s="1" t="n"/>
+      <c r="JB1" s="1" t="n"/>
+      <c r="JC1" s="1" t="n"/>
+      <c r="JD1" s="1" t="n"/>
+      <c r="JE1" s="1" t="n"/>
+      <c r="JF1" s="1" t="n"/>
+      <c r="JG1" s="1" t="n"/>
+      <c r="JH1" s="1" t="n"/>
+      <c r="JI1" s="1" t="n"/>
+      <c r="JJ1" s="1" t="n"/>
+      <c r="JK1" s="1" t="n"/>
+      <c r="JL1" s="1" t="n"/>
+      <c r="JM1" s="1" t="n"/>
+      <c r="JN1" s="1" t="n"/>
+      <c r="JO1" s="1" t="n"/>
+      <c r="JP1" s="1" t="n"/>
+      <c r="JQ1" s="1" t="n"/>
+      <c r="JR1" s="1" t="n"/>
+      <c r="JS1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1851,13 +1805,13 @@
           <t>Dose</t>
         </is>
       </c>
-      <c r="E2" s="26" t="n"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="G2" s="26" t="n"/>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Study Phase</t>
@@ -1868,7 +1822,7 @@
           <t>Period of Study</t>
         </is>
       </c>
-      <c r="J2" s="26" t="n"/>
+      <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Total Cohort (N)</t>
@@ -1884,29 +1838,29 @@
           <t>Age</t>
         </is>
       </c>
-      <c r="N2" s="25" t="n"/>
-      <c r="O2" s="26" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Drug Naive</t>
         </is>
       </c>
-      <c r="Q2" s="25" t="n"/>
-      <c r="R2" s="26" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Treated</t>
         </is>
       </c>
-      <c r="T2" s="25" t="n"/>
-      <c r="U2" s="26" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Hba1C Run In</t>
         </is>
       </c>
-      <c r="W2" s="25" t="n"/>
-      <c r="X2" s="26" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Type 2 Diabetes Diagnosis</t>
@@ -1987,433 +1941,433 @@
           <t>Male Stratum</t>
         </is>
       </c>
-      <c r="AO2" s="26" t="n"/>
+      <c r="AO2" s="2" t="n"/>
       <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>Female Stratum</t>
         </is>
       </c>
-      <c r="AQ2" s="26" t="n"/>
+      <c r="AQ2" s="2" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="AS2" s="26" t="n"/>
+      <c r="AS2" s="2" t="n"/>
       <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>sex: male</t>
         </is>
       </c>
-      <c r="AU2" s="25" t="n"/>
-      <c r="AV2" s="25" t="n"/>
-      <c r="AW2" s="25" t="n"/>
-      <c r="AX2" s="26" t="n"/>
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="2" t="n"/>
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
       <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="AZ2" s="25" t="n"/>
-      <c r="BA2" s="25" t="n"/>
-      <c r="BB2" s="25" t="n"/>
-      <c r="BC2" s="26" t="n"/>
+      <c r="AZ2" s="2" t="n"/>
+      <c r="BA2" s="2" t="n"/>
+      <c r="BB2" s="2" t="n"/>
+      <c r="BC2" s="2" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>body_weight</t>
         </is>
       </c>
-      <c r="BE2" s="25" t="n"/>
-      <c r="BF2" s="25" t="n"/>
-      <c r="BG2" s="25" t="n"/>
-      <c r="BH2" s="26" t="n"/>
+      <c r="BE2" s="2" t="n"/>
+      <c r="BF2" s="2" t="n"/>
+      <c r="BG2" s="2" t="n"/>
+      <c r="BH2" s="2" t="n"/>
       <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
-      <c r="BK2" s="25" t="n"/>
-      <c r="BL2" s="25" t="n"/>
-      <c r="BM2" s="26" t="n"/>
+      <c r="BJ2" s="2" t="n"/>
+      <c r="BK2" s="2" t="n"/>
+      <c r="BL2" s="2" t="n"/>
+      <c r="BM2" s="2" t="n"/>
       <c r="BN2" s="2" t="inlineStr">
         <is>
           <t>hba1c</t>
         </is>
       </c>
-      <c r="BO2" s="25" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="25" t="n"/>
-      <c r="BR2" s="26" t="n"/>
+      <c r="BO2" s="2" t="n"/>
+      <c r="BP2" s="2" t="n"/>
+      <c r="BQ2" s="2" t="n"/>
+      <c r="BR2" s="2" t="n"/>
       <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>fasting plasma glucose</t>
         </is>
       </c>
-      <c r="BT2" s="25" t="n"/>
-      <c r="BU2" s="25" t="n"/>
-      <c r="BV2" s="25" t="n"/>
-      <c r="BW2" s="26" t="n"/>
+      <c r="BT2" s="2" t="n"/>
+      <c r="BU2" s="2" t="n"/>
+      <c r="BV2" s="2" t="n"/>
+      <c r="BW2" s="2" t="n"/>
       <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>ppg auc1-4h</t>
         </is>
       </c>
-      <c r="BY2" s="25" t="n"/>
-      <c r="BZ2" s="25" t="n"/>
-      <c r="CA2" s="25" t="n"/>
-      <c r="CB2" s="26" t="n"/>
+      <c r="BY2" s="2" t="n"/>
+      <c r="BZ2" s="2" t="n"/>
+      <c r="CA2" s="2" t="n"/>
+      <c r="CB2" s="2" t="n"/>
       <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>24-hour mean glucose</t>
         </is>
       </c>
-      <c r="CD2" s="25" t="n"/>
-      <c r="CE2" s="25" t="n"/>
-      <c r="CF2" s="25" t="n"/>
-      <c r="CG2" s="26" t="n"/>
+      <c r="CD2" s="2" t="n"/>
+      <c r="CE2" s="2" t="n"/>
+      <c r="CF2" s="2" t="n"/>
+      <c r="CG2" s="2" t="n"/>
       <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="CI2" s="25" t="n"/>
-      <c r="CJ2" s="25" t="n"/>
-      <c r="CK2" s="25" t="n"/>
-      <c r="CL2" s="26" t="n"/>
+      <c r="CI2" s="2" t="n"/>
+      <c r="CJ2" s="2" t="n"/>
+      <c r="CK2" s="2" t="n"/>
+      <c r="CL2" s="2" t="n"/>
       <c r="CM2" s="2" t="inlineStr">
         <is>
           <t>egfr</t>
         </is>
       </c>
-      <c r="CN2" s="25" t="n"/>
-      <c r="CO2" s="25" t="n"/>
-      <c r="CP2" s="25" t="n"/>
-      <c r="CQ2" s="26" t="n"/>
+      <c r="CN2" s="2" t="n"/>
+      <c r="CO2" s="2" t="n"/>
+      <c r="CP2" s="2" t="n"/>
+      <c r="CQ2" s="2" t="n"/>
       <c r="CR2" s="2" t="inlineStr">
         <is>
           <t>systolic blood pressure</t>
         </is>
       </c>
-      <c r="CS2" s="25" t="n"/>
-      <c r="CT2" s="25" t="n"/>
-      <c r="CU2" s="25" t="n"/>
-      <c r="CV2" s="26" t="n"/>
+      <c r="CS2" s="2" t="n"/>
+      <c r="CT2" s="2" t="n"/>
+      <c r="CU2" s="2" t="n"/>
+      <c r="CV2" s="2" t="n"/>
       <c r="CW2" s="2" t="inlineStr">
         <is>
           <t>diastolic blood pressure</t>
         </is>
       </c>
-      <c r="CX2" s="25" t="n"/>
-      <c r="CY2" s="25" t="n"/>
-      <c r="CZ2" s="25" t="n"/>
-      <c r="DA2" s="26" t="n"/>
+      <c r="CX2" s="2" t="n"/>
+      <c r="CY2" s="2" t="n"/>
+      <c r="CZ2" s="2" t="n"/>
+      <c r="DA2" s="2" t="n"/>
       <c r="DB2" s="2" t="inlineStr">
         <is>
           <t>insulin auc1-4h</t>
         </is>
       </c>
-      <c r="DC2" s="25" t="n"/>
-      <c r="DD2" s="25" t="n"/>
-      <c r="DE2" s="25" t="n"/>
-      <c r="DF2" s="26" t="n"/>
+      <c r="DC2" s="2" t="n"/>
+      <c r="DD2" s="2" t="n"/>
+      <c r="DE2" s="2" t="n"/>
+      <c r="DF2" s="2" t="n"/>
       <c r="DG2" s="2" t="inlineStr">
         <is>
           <t>insulin auc10-13h</t>
         </is>
       </c>
-      <c r="DH2" s="25" t="n"/>
-      <c r="DI2" s="25" t="n"/>
-      <c r="DJ2" s="25" t="n"/>
-      <c r="DK2" s="26" t="n"/>
+      <c r="DH2" s="2" t="n"/>
+      <c r="DI2" s="2" t="n"/>
+      <c r="DJ2" s="2" t="n"/>
+      <c r="DK2" s="2" t="n"/>
       <c r="DL2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (fasting)</t>
         </is>
       </c>
-      <c r="DM2" s="25" t="n"/>
-      <c r="DN2" s="25" t="n"/>
-      <c r="DO2" s="25" t="n"/>
-      <c r="DP2" s="26" t="n"/>
+      <c r="DM2" s="2" t="n"/>
+      <c r="DN2" s="2" t="n"/>
+      <c r="DO2" s="2" t="n"/>
+      <c r="DP2" s="2" t="n"/>
       <c r="DQ2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (24h)</t>
         </is>
       </c>
-      <c r="DR2" s="25" t="n"/>
-      <c r="DS2" s="25" t="n"/>
-      <c r="DT2" s="25" t="n"/>
-      <c r="DU2" s="26" t="n"/>
+      <c r="DR2" s="2" t="n"/>
+      <c r="DS2" s="2" t="n"/>
+      <c r="DT2" s="2" t="n"/>
+      <c r="DU2" s="2" t="n"/>
       <c r="DV2" s="2" t="inlineStr">
         <is>
           <t>total_cholesterol</t>
         </is>
       </c>
-      <c r="DW2" s="25" t="n"/>
-      <c r="DX2" s="25" t="n"/>
-      <c r="DY2" s="25" t="n"/>
-      <c r="DZ2" s="26" t="n"/>
+      <c r="DW2" s="2" t="n"/>
+      <c r="DX2" s="2" t="n"/>
+      <c r="DY2" s="2" t="n"/>
+      <c r="DZ2" s="2" t="n"/>
       <c r="EA2" s="2" t="inlineStr">
         <is>
           <t>hdl-c</t>
         </is>
       </c>
-      <c r="EB2" s="25" t="n"/>
-      <c r="EC2" s="25" t="n"/>
-      <c r="ED2" s="25" t="n"/>
-      <c r="EE2" s="26" t="n"/>
+      <c r="EB2" s="2" t="n"/>
+      <c r="EC2" s="2" t="n"/>
+      <c r="ED2" s="2" t="n"/>
+      <c r="EE2" s="2" t="n"/>
       <c r="EF2" s="2" t="inlineStr">
         <is>
           <t>ldl-c</t>
         </is>
       </c>
-      <c r="EG2" s="25" t="n"/>
-      <c r="EH2" s="25" t="n"/>
-      <c r="EI2" s="25" t="n"/>
-      <c r="EJ2" s="26" t="n"/>
+      <c r="EG2" s="2" t="n"/>
+      <c r="EH2" s="2" t="n"/>
+      <c r="EI2" s="2" t="n"/>
+      <c r="EJ2" s="2" t="n"/>
       <c r="EK2" s="2" t="inlineStr">
         <is>
           <t>triglycerides</t>
         </is>
       </c>
-      <c r="EL2" s="25" t="n"/>
-      <c r="EM2" s="25" t="n"/>
-      <c r="EN2" s="25" t="n"/>
-      <c r="EO2" s="26" t="n"/>
+      <c r="EL2" s="2" t="n"/>
+      <c r="EM2" s="2" t="n"/>
+      <c r="EN2" s="2" t="n"/>
+      <c r="EO2" s="2" t="n"/>
       <c r="EP2" s="2" t="inlineStr">
         <is>
           <t>free fatty acids</t>
         </is>
       </c>
-      <c r="EQ2" s="25" t="n"/>
-      <c r="ER2" s="25" t="n"/>
-      <c r="ES2" s="25" t="n"/>
-      <c r="ET2" s="26" t="n"/>
+      <c r="EQ2" s="2" t="n"/>
+      <c r="ER2" s="2" t="n"/>
+      <c r="ES2" s="2" t="n"/>
+      <c r="ET2" s="2" t="n"/>
       <c r="EU2" s="2" t="inlineStr">
         <is>
           <t>total ketone bodies</t>
         </is>
       </c>
-      <c r="EV2" s="25" t="n"/>
-      <c r="EW2" s="25" t="n"/>
-      <c r="EX2" s="25" t="n"/>
-      <c r="EY2" s="26" t="n"/>
+      <c r="EV2" s="2" t="n"/>
+      <c r="EW2" s="2" t="n"/>
+      <c r="EX2" s="2" t="n"/>
+      <c r="EY2" s="2" t="n"/>
       <c r="EZ2" s="2" t="inlineStr">
         <is>
           <t>sex: female</t>
         </is>
       </c>
-      <c r="FA2" s="25" t="n"/>
-      <c r="FB2" s="25" t="n"/>
-      <c r="FC2" s="25" t="n"/>
-      <c r="FD2" s="26" t="n"/>
+      <c r="FA2" s="2" t="n"/>
+      <c r="FB2" s="2" t="n"/>
+      <c r="FC2" s="2" t="n"/>
+      <c r="FD2" s="2" t="n"/>
       <c r="FE2" s="2" t="inlineStr">
         <is>
           <t>race: asian (japanese)</t>
         </is>
       </c>
-      <c r="FF2" s="25" t="n"/>
-      <c r="FG2" s="25" t="n"/>
-      <c r="FH2" s="25" t="n"/>
-      <c r="FI2" s="26" t="n"/>
+      <c r="FF2" s="2" t="n"/>
+      <c r="FG2" s="2" t="n"/>
+      <c r="FH2" s="2" t="n"/>
+      <c r="FI2" s="2" t="n"/>
       <c r="FJ2" s="2" t="inlineStr">
         <is>
           <t>insulin auc1-4h</t>
         </is>
       </c>
-      <c r="FK2" s="25" t="n"/>
-      <c r="FL2" s="25" t="n"/>
-      <c r="FM2" s="25" t="n"/>
-      <c r="FN2" s="25" t="n"/>
-      <c r="FO2" s="26" t="n"/>
+      <c r="FK2" s="2" t="n"/>
+      <c r="FL2" s="2" t="n"/>
+      <c r="FM2" s="2" t="n"/>
+      <c r="FN2" s="2" t="n"/>
+      <c r="FO2" s="2" t="n"/>
       <c r="FP2" s="2" t="inlineStr">
         <is>
           <t>insulin auc10-13h</t>
         </is>
       </c>
-      <c r="FQ2" s="25" t="n"/>
-      <c r="FR2" s="25" t="n"/>
-      <c r="FS2" s="25" t="n"/>
-      <c r="FT2" s="25" t="n"/>
-      <c r="FU2" s="26" t="n"/>
+      <c r="FQ2" s="2" t="n"/>
+      <c r="FR2" s="2" t="n"/>
+      <c r="FS2" s="2" t="n"/>
+      <c r="FT2" s="2" t="n"/>
+      <c r="FU2" s="2" t="n"/>
       <c r="FV2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (fasting)</t>
         </is>
       </c>
-      <c r="FW2" s="25" t="n"/>
-      <c r="FX2" s="25" t="n"/>
-      <c r="FY2" s="25" t="n"/>
-      <c r="FZ2" s="25" t="n"/>
-      <c r="GA2" s="26" t="n"/>
+      <c r="FW2" s="2" t="n"/>
+      <c r="FX2" s="2" t="n"/>
+      <c r="FY2" s="2" t="n"/>
+      <c r="FZ2" s="2" t="n"/>
+      <c r="GA2" s="2" t="n"/>
       <c r="GB2" s="2" t="inlineStr">
         <is>
           <t>8-iso-pgf2a (24h)</t>
         </is>
       </c>
-      <c r="GC2" s="25" t="n"/>
-      <c r="GD2" s="25" t="n"/>
-      <c r="GE2" s="25" t="n"/>
-      <c r="GF2" s="25" t="n"/>
-      <c r="GG2" s="26" t="n"/>
+      <c r="GC2" s="2" t="n"/>
+      <c r="GD2" s="2" t="n"/>
+      <c r="GE2" s="2" t="n"/>
+      <c r="GF2" s="2" t="n"/>
+      <c r="GG2" s="2" t="n"/>
       <c r="GH2" s="2" t="inlineStr">
         <is>
           <t>total_cholesterol</t>
         </is>
       </c>
-      <c r="GI2" s="25" t="n"/>
-      <c r="GJ2" s="25" t="n"/>
-      <c r="GK2" s="25" t="n"/>
-      <c r="GL2" s="25" t="n"/>
-      <c r="GM2" s="26" t="n"/>
+      <c r="GI2" s="2" t="n"/>
+      <c r="GJ2" s="2" t="n"/>
+      <c r="GK2" s="2" t="n"/>
+      <c r="GL2" s="2" t="n"/>
+      <c r="GM2" s="2" t="n"/>
       <c r="GN2" s="2" t="inlineStr">
         <is>
           <t>hdl-c</t>
         </is>
       </c>
-      <c r="GO2" s="25" t="n"/>
-      <c r="GP2" s="25" t="n"/>
-      <c r="GQ2" s="25" t="n"/>
-      <c r="GR2" s="25" t="n"/>
-      <c r="GS2" s="26" t="n"/>
+      <c r="GO2" s="2" t="n"/>
+      <c r="GP2" s="2" t="n"/>
+      <c r="GQ2" s="2" t="n"/>
+      <c r="GR2" s="2" t="n"/>
+      <c r="GS2" s="2" t="n"/>
       <c r="GT2" s="2" t="inlineStr">
         <is>
           <t>ldl-c</t>
         </is>
       </c>
-      <c r="GU2" s="25" t="n"/>
-      <c r="GV2" s="25" t="n"/>
-      <c r="GW2" s="25" t="n"/>
-      <c r="GX2" s="25" t="n"/>
-      <c r="GY2" s="26" t="n"/>
+      <c r="GU2" s="2" t="n"/>
+      <c r="GV2" s="2" t="n"/>
+      <c r="GW2" s="2" t="n"/>
+      <c r="GX2" s="2" t="n"/>
+      <c r="GY2" s="2" t="n"/>
       <c r="GZ2" s="2" t="inlineStr">
         <is>
           <t>triglycerides</t>
         </is>
       </c>
-      <c r="HA2" s="25" t="n"/>
-      <c r="HB2" s="25" t="n"/>
-      <c r="HC2" s="25" t="n"/>
-      <c r="HD2" s="25" t="n"/>
-      <c r="HE2" s="26" t="n"/>
+      <c r="HA2" s="2" t="n"/>
+      <c r="HB2" s="2" t="n"/>
+      <c r="HC2" s="2" t="n"/>
+      <c r="HD2" s="2" t="n"/>
+      <c r="HE2" s="2" t="n"/>
       <c r="HF2" s="2" t="inlineStr">
         <is>
           <t>free fatty acids</t>
         </is>
       </c>
-      <c r="HG2" s="25" t="n"/>
-      <c r="HH2" s="25" t="n"/>
-      <c r="HI2" s="25" t="n"/>
-      <c r="HJ2" s="25" t="n"/>
-      <c r="HK2" s="26" t="n"/>
+      <c r="HG2" s="2" t="n"/>
+      <c r="HH2" s="2" t="n"/>
+      <c r="HI2" s="2" t="n"/>
+      <c r="HJ2" s="2" t="n"/>
+      <c r="HK2" s="2" t="n"/>
       <c r="HL2" s="2" t="inlineStr">
         <is>
           <t>total ketone bodies</t>
         </is>
       </c>
-      <c r="HM2" s="25" t="n"/>
-      <c r="HN2" s="25" t="n"/>
-      <c r="HO2" s="25" t="n"/>
-      <c r="HP2" s="25" t="n"/>
-      <c r="HQ2" s="26" t="n"/>
+      <c r="HM2" s="2" t="n"/>
+      <c r="HN2" s="2" t="n"/>
+      <c r="HO2" s="2" t="n"/>
+      <c r="HP2" s="2" t="n"/>
+      <c r="HQ2" s="2" t="n"/>
       <c r="HR2" s="2" t="inlineStr">
         <is>
           <t>ppg auc1-4h</t>
         </is>
       </c>
-      <c r="HS2" s="25" t="n"/>
-      <c r="HT2" s="25" t="n"/>
-      <c r="HU2" s="25" t="n"/>
-      <c r="HV2" s="25" t="n"/>
-      <c r="HW2" s="26" t="n"/>
+      <c r="HS2" s="2" t="n"/>
+      <c r="HT2" s="2" t="n"/>
+      <c r="HU2" s="2" t="n"/>
+      <c r="HV2" s="2" t="n"/>
+      <c r="HW2" s="2" t="n"/>
       <c r="HX2" s="2" t="inlineStr">
         <is>
           <t>fasting plasma glucose</t>
         </is>
       </c>
-      <c r="HY2" s="25" t="n"/>
-      <c r="HZ2" s="25" t="n"/>
-      <c r="IA2" s="25" t="n"/>
-      <c r="IB2" s="25" t="n"/>
-      <c r="IC2" s="26" t="n"/>
+      <c r="HY2" s="2" t="n"/>
+      <c r="HZ2" s="2" t="n"/>
+      <c r="IA2" s="2" t="n"/>
+      <c r="IB2" s="2" t="n"/>
+      <c r="IC2" s="2" t="n"/>
       <c r="ID2" s="2" t="inlineStr">
         <is>
           <t>24-hour mean glucose</t>
         </is>
       </c>
-      <c r="IE2" s="25" t="n"/>
-      <c r="IF2" s="25" t="n"/>
-      <c r="IG2" s="25" t="n"/>
-      <c r="IH2" s="25" t="n"/>
-      <c r="II2" s="26" t="n"/>
+      <c r="IE2" s="2" t="n"/>
+      <c r="IF2" s="2" t="n"/>
+      <c r="IG2" s="2" t="n"/>
+      <c r="IH2" s="2" t="n"/>
+      <c r="II2" s="2" t="n"/>
       <c r="IJ2" s="2" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="IK2" s="25" t="n"/>
-      <c r="IL2" s="25" t="n"/>
-      <c r="IM2" s="25" t="n"/>
-      <c r="IN2" s="25" t="n"/>
-      <c r="IO2" s="26" t="n"/>
+      <c r="IK2" s="2" t="n"/>
+      <c r="IL2" s="2" t="n"/>
+      <c r="IM2" s="2" t="n"/>
+      <c r="IN2" s="2" t="n"/>
+      <c r="IO2" s="2" t="n"/>
       <c r="IP2" s="2" t="inlineStr">
         <is>
           <t>hba1c</t>
         </is>
       </c>
-      <c r="IQ2" s="25" t="n"/>
-      <c r="IR2" s="25" t="n"/>
-      <c r="IS2" s="25" t="n"/>
-      <c r="IT2" s="25" t="n"/>
-      <c r="IU2" s="26" t="n"/>
+      <c r="IQ2" s="2" t="n"/>
+      <c r="IR2" s="2" t="n"/>
+      <c r="IS2" s="2" t="n"/>
+      <c r="IT2" s="2" t="n"/>
+      <c r="IU2" s="2" t="n"/>
       <c r="IV2" s="2" t="inlineStr">
         <is>
-          <t>any adverse event</t>
-        </is>
-      </c>
-      <c r="IW2" s="25" t="n"/>
-      <c r="IX2" s="25" t="n"/>
-      <c r="IY2" s="26" t="n"/>
+          <t>Any Adverse Event</t>
+        </is>
+      </c>
+      <c r="IW2" s="2" t="n"/>
+      <c r="IX2" s="2" t="n"/>
+      <c r="IY2" s="2" t="n"/>
       <c r="IZ2" s="2" t="inlineStr">
         <is>
           <t>severe adverse events</t>
         </is>
       </c>
-      <c r="JA2" s="25" t="n"/>
-      <c r="JB2" s="25" t="n"/>
-      <c r="JC2" s="26" t="n"/>
+      <c r="JA2" s="2" t="n"/>
+      <c r="JB2" s="2" t="n"/>
+      <c r="JC2" s="2" t="n"/>
       <c r="JD2" s="2" t="inlineStr">
         <is>
           <t>serious adverse events</t>
         </is>
       </c>
-      <c r="JE2" s="25" t="n"/>
-      <c r="JF2" s="25" t="n"/>
-      <c r="JG2" s="26" t="n"/>
+      <c r="JE2" s="2" t="n"/>
+      <c r="JF2" s="2" t="n"/>
+      <c r="JG2" s="2" t="n"/>
       <c r="JH2" s="2" t="inlineStr">
         <is>
           <t>discontinuation due to adverse events</t>
         </is>
       </c>
-      <c r="JI2" s="25" t="n"/>
-      <c r="JJ2" s="25" t="n"/>
-      <c r="JK2" s="26" t="n"/>
+      <c r="JI2" s="2" t="n"/>
+      <c r="JJ2" s="2" t="n"/>
+      <c r="JK2" s="2" t="n"/>
       <c r="JL2" s="2" t="inlineStr">
         <is>
           <t>hypoglycemia</t>
         </is>
       </c>
-      <c r="JM2" s="25" t="n"/>
-      <c r="JN2" s="25" t="n"/>
-      <c r="JO2" s="26" t="n"/>
+      <c r="JM2" s="2" t="n"/>
+      <c r="JN2" s="2" t="n"/>
+      <c r="JO2" s="2" t="n"/>
       <c r="JP2" s="2" t="inlineStr">
         <is>
           <t>genital infection</t>
         </is>
       </c>
-      <c r="JQ2" s="25" t="n"/>
-      <c r="JR2" s="25" t="n"/>
-      <c r="JS2" s="26" t="n"/>
+      <c r="JQ2" s="2" t="n"/>
+      <c r="JR2" s="2" t="n"/>
+      <c r="JS2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
@@ -4264,7 +4218,11 @@
       <c r="FK4" s="6" t="n"/>
       <c r="FL4" s="6" t="n"/>
       <c r="FM4" s="6" t="n"/>
-      <c r="FN4" s="6" t="n"/>
+      <c r="FN4" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO4" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -4274,7 +4232,11 @@
       <c r="FQ4" s="6" t="n"/>
       <c r="FR4" s="6" t="n"/>
       <c r="FS4" s="6" t="n"/>
-      <c r="FT4" s="6" t="n"/>
+      <c r="FT4" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU4" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -4382,88 +4344,124 @@
       <c r="IS4" s="6" t="n"/>
       <c r="IT4" s="6" t="n"/>
       <c r="IU4" s="6" t="n"/>
-      <c r="IV4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="IW4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="IX4" s="6" t="n">
-        <v>9.5</v>
+      <c r="IV4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="JB4" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="JF4" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="JJ4" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="JN4" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ4" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="JR4" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS4" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5045,88 +5043,124 @@
       <c r="IS5" s="8" t="n"/>
       <c r="IT5" s="8" t="n"/>
       <c r="IU5" s="8" t="n"/>
-      <c r="IV5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="IW5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="IX5" s="8" t="n">
-        <v>9.5</v>
+      <c r="IV5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JB5" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JF5" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JJ5" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JN5" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ5" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JR5" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS5" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5648,11 @@
       <c r="FK6" s="6" t="n"/>
       <c r="FL6" s="6" t="n"/>
       <c r="FM6" s="6" t="n"/>
-      <c r="FN6" s="6" t="n"/>
+      <c r="FN6" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO6" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -5624,7 +5662,11 @@
       <c r="FQ6" s="6" t="n"/>
       <c r="FR6" s="6" t="n"/>
       <c r="FS6" s="6" t="n"/>
-      <c r="FT6" s="6" t="n"/>
+      <c r="FT6" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU6" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -6383,7 +6425,11 @@
       <c r="HA7" s="8" t="n"/>
       <c r="HB7" s="8" t="n"/>
       <c r="HC7" s="8" t="n"/>
-      <c r="HD7" s="8" t="n"/>
+      <c r="HD7" s="8" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="HE7" s="8" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -6463,88 +6509,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="IW7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="IX7" s="8" t="n">
-        <v>9.5</v>
+      <c r="IV7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JB7" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JF7" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JJ7" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JN7" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ7" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JR7" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS7" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7114,11 @@
       <c r="FK8" s="6" t="n"/>
       <c r="FL8" s="6" t="n"/>
       <c r="FM8" s="6" t="n"/>
-      <c r="FN8" s="6" t="n"/>
+      <c r="FN8" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO8" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -7042,7 +7128,11 @@
       <c r="FQ8" s="6" t="n"/>
       <c r="FR8" s="6" t="n"/>
       <c r="FS8" s="6" t="n"/>
-      <c r="FT8" s="6" t="n"/>
+      <c r="FT8" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU8" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -7150,88 +7240,124 @@
       <c r="IS8" s="6" t="n"/>
       <c r="IT8" s="6" t="n"/>
       <c r="IU8" s="6" t="n"/>
-      <c r="IV8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="IX8" s="6" t="n">
-        <v>15</v>
+      <c r="IV8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="JB8" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="JF8" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="JJ8" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="JN8" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ8" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="JR8" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS8" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7813,88 +7939,124 @@
       <c r="IS9" s="8" t="n"/>
       <c r="IT9" s="8" t="n"/>
       <c r="IU9" s="8" t="n"/>
-      <c r="IV9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="IX9" s="8" t="n">
-        <v>15</v>
+      <c r="IV9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JB9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JF9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JJ9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JN9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ9" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JR9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8544,11 @@
       <c r="FK10" s="6" t="n"/>
       <c r="FL10" s="6" t="n"/>
       <c r="FM10" s="6" t="n"/>
-      <c r="FN10" s="6" t="n"/>
+      <c r="FN10" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO10" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -8392,7 +8558,11 @@
       <c r="FQ10" s="6" t="n"/>
       <c r="FR10" s="6" t="n"/>
       <c r="FS10" s="6" t="n"/>
-      <c r="FT10" s="6" t="n"/>
+      <c r="FT10" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU10" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -9151,7 +9321,11 @@
       <c r="HA11" s="8" t="n"/>
       <c r="HB11" s="8" t="n"/>
       <c r="HC11" s="8" t="n"/>
-      <c r="HD11" s="8" t="n"/>
+      <c r="HD11" s="8" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="HE11" s="8" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -9231,88 +9405,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="IX11" s="8" t="n">
-        <v>15</v>
+      <c r="IV11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JB11" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JF11" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JJ11" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JN11" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JR11" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS11" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9800,7 +10010,11 @@
       <c r="FK12" s="6" t="n"/>
       <c r="FL12" s="6" t="n"/>
       <c r="FM12" s="6" t="n"/>
-      <c r="FN12" s="6" t="n"/>
+      <c r="FN12" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO12" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -9810,7 +10024,11 @@
       <c r="FQ12" s="6" t="n"/>
       <c r="FR12" s="6" t="n"/>
       <c r="FS12" s="6" t="n"/>
-      <c r="FT12" s="6" t="n"/>
+      <c r="FT12" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU12" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -9918,88 +10136,124 @@
       <c r="IS12" s="6" t="n"/>
       <c r="IT12" s="6" t="n"/>
       <c r="IU12" s="6" t="n"/>
-      <c r="IV12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="IX12" s="6" t="n">
-        <v>15.8</v>
+      <c r="IV12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="JB12" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="JF12" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="JJ12" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="JN12" s="6" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="JQ12" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="JR12" s="6" t="n">
-        <v>5.3</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10581,88 +10835,124 @@
       <c r="IS13" s="8" t="n"/>
       <c r="IT13" s="8" t="n"/>
       <c r="IU13" s="8" t="n"/>
-      <c r="IV13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="IX13" s="8" t="n">
-        <v>15.8</v>
+      <c r="IV13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JB13" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JF13" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JJ13" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JN13" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="JQ13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JR13" s="8" t="n">
-        <v>5.3</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS13" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11440,11 @@
       <c r="FK14" s="6" t="n"/>
       <c r="FL14" s="6" t="n"/>
       <c r="FM14" s="6" t="n"/>
-      <c r="FN14" s="6" t="n"/>
+      <c r="FN14" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FO14" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -11160,7 +11454,11 @@
       <c r="FQ14" s="6" t="n"/>
       <c r="FR14" s="6" t="n"/>
       <c r="FS14" s="6" t="n"/>
-      <c r="FT14" s="6" t="n"/>
+      <c r="FT14" s="6" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="FU14" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -11919,7 +12217,11 @@
       <c r="HA15" s="8" t="n"/>
       <c r="HB15" s="8" t="n"/>
       <c r="HC15" s="8" t="n"/>
-      <c r="HD15" s="8" t="n"/>
+      <c r="HD15" s="8" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
       <c r="HE15" s="8" t="inlineStr">
         <is>
           <t>ratio</t>
@@ -11999,88 +12301,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV15" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="IX15" s="8" t="n">
-        <v>15.8</v>
+      <c r="IV15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JB15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JF15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JJ15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JN15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="JQ15" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JR15" s="8" t="n">
-        <v>5.3</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12189,6 +12527,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -29134,6 +29473,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -30441,6 +30781,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -33544,6 +33885,8 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
@@ -34803,6 +35146,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -43524,6 +43868,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -43555,6 +43900,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
@@ -43606,6 +43952,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
@@ -43661,6 +44008,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -43756,6 +44104,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -44135,6 +44484,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -44191,6 +44541,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -44262,6 +44613,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
@@ -44379,6 +44731,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -44440,6 +44793,8 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
@@ -44834,6 +45189,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -45308,7 +45664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -45328,6 +45684,9 @@
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="65" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -45416,6 +45775,21 @@
           <t>source_page</t>
         </is>
       </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>variable_role</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>applicable_population</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>assessment_stage</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -45480,6 +45854,21 @@
       </c>
       <c r="Q2" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -45526,6 +45915,21 @@
       <c r="Q3" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -45591,6 +45995,21 @@
       <c r="Q4" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>drug_naive</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -45656,6 +46075,21 @@
       <c r="Q5" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>previously_treated</t>
+        </is>
+      </c>
+      <c r="T5" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -45720,6 +46154,21 @@
       </c>
       <c r="Q6" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>run_in</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>run_in</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -45766,6 +46215,21 @@
       <c r="Q7" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T7" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -45811,6 +46275,21 @@
       <c r="Q8" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -45856,6 +46335,21 @@
       <c r="Q9" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -45901,6 +46395,21 @@
       <c r="Q10" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -45950,6 +46459,21 @@
       <c r="Q11" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -45999,6 +46523,21 @@
       <c r="Q12" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -46048,6 +46587,21 @@
       <c r="Q13" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -46097,6 +46651,21 @@
       <c r="Q14" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T14" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -46146,6 +46715,21 @@
       <c r="Q15" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -46195,6 +46779,21 @@
       <c r="Q16" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T16" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -46243,6 +46842,21 @@
       </c>
       <c r="Q17" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T17" s="10" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -46288,6 +46902,21 @@
       </c>
       <c r="Q18" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>INCLUSION_CRITERION</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T18" s="10" t="inlineStr">
+        <is>
+          <t>eligibility_assessment</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -46302,7 +46931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM154"/>
+  <dimension ref="A1:AS154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -46344,6 +46973,12 @@
     <col width="14" customWidth="1" min="37" max="37"/>
     <col width="60" customWidth="1" min="38" max="38"/>
     <col width="65" customWidth="1" min="39" max="39"/>
+    <col width="26" customWidth="1" min="40" max="40"/>
+    <col width="32" customWidth="1" min="41" max="41"/>
+    <col width="28" customWidth="1" min="42" max="42"/>
+    <col width="24" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="65" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -46540,6 +47175,36 @@
       <c r="AM1" s="9" t="inlineStr">
         <is>
           <t>raw_source_text</t>
+        </is>
+      </c>
+      <c r="AN1" s="9" t="inlineStr">
+        <is>
+          <t>variable_role</t>
+        </is>
+      </c>
+      <c r="AO1" s="9" t="inlineStr">
+        <is>
+          <t>estimate_type</t>
+        </is>
+      </c>
+      <c r="AP1" s="9" t="inlineStr">
+        <is>
+          <t>original_timepoint_label</t>
+        </is>
+      </c>
+      <c r="AQ1" s="9" t="inlineStr">
+        <is>
+          <t>assessment_stage</t>
+        </is>
+      </c>
+      <c r="AR1" s="9" t="inlineStr">
+        <is>
+          <t>timepoint_type</t>
+        </is>
+      </c>
+      <c r="AS1" s="9" t="inlineStr">
+        <is>
+          <t>source_evidence</t>
         </is>
       </c>
     </row>
@@ -46651,6 +47316,36 @@
           <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
         </is>
       </c>
+      <c r="AN2" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO2" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP2" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ2" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR2" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS2" s="10" t="inlineStr">
+        <is>
+          <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -46760,6 +47455,36 @@
           <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
         </is>
       </c>
+      <c r="AN3" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO3" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP3" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ3" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR3" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS3" s="10" t="inlineStr">
+        <is>
+          <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -46869,6 +47594,36 @@
           <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
         </is>
       </c>
+      <c r="AN4" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO4" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP4" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ4" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR4" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS4" s="10" t="inlineStr">
+        <is>
+          <t>Male 17 (81.0) 14 (70.0) 16 (84.2)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -46976,6 +47731,36 @@
           <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
         </is>
       </c>
+      <c r="AN5" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP5" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR5" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -47083,6 +47868,36 @@
           <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
         </is>
       </c>
+      <c r="AN6" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP6" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR6" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -47190,6 +48005,36 @@
           <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
         </is>
       </c>
+      <c r="AN7" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP7" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR7" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>Age (years) 60.7 (10.8) 64.8 (5.9) 62.6 (7.8)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -47297,6 +48142,36 @@
           <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
         </is>
       </c>
+      <c r="AN8" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP8" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR8" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -47404,6 +48279,36 @@
           <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
         </is>
       </c>
+      <c r="AN9" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP9" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR9" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -47511,6 +48416,36 @@
           <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
         </is>
       </c>
+      <c r="AN10" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP10" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR10" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>Body weight (kg) 67.7 (10.0) 63.5 (10.6) 65.9 (12.1)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -47618,6 +48553,36 @@
           <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
         </is>
       </c>
+      <c r="AN11" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP11" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR11" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -47725,6 +48690,36 @@
           <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
         </is>
       </c>
+      <c r="AN12" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP12" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR12" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -47832,6 +48827,36 @@
           <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
         </is>
       </c>
+      <c r="AN13" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP13" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR13" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>Body mass index (kg/m 2) 24.9 (2.8) 24.1 (3.7) 24.0 (3.2)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -47939,6 +48964,36 @@
           <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
         </is>
       </c>
+      <c r="AN14" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP14" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR14" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -48046,6 +49101,36 @@
           <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
         </is>
       </c>
+      <c r="AN15" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP15" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR15" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -48153,6 +49238,36 @@
           <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
         </is>
       </c>
+      <c r="AN16" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP16" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR16" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>HbA1c (%) 8.00 (0.82) 7.99 (0.83) 7.73 (0.75)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -48260,6 +49375,36 @@
           <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
         </is>
       </c>
+      <c r="AN17" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP17" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR17" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS17" s="10" t="inlineStr">
+        <is>
+          <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -48367,6 +49512,36 @@
           <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
         </is>
       </c>
+      <c r="AN18" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP18" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ18" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR18" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS18" s="10" t="inlineStr">
+        <is>
+          <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -48474,6 +49649,36 @@
           <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
         </is>
       </c>
+      <c r="AN19" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO19" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP19" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ19" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR19" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS19" s="10" t="inlineStr">
+        <is>
+          <t>Fasting plasma glucose (mg/dl)* 154.5 (19.8) 151.0 (21.6) 151.9 (23.3)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -48581,6 +49786,36 @@
           <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
         </is>
       </c>
+      <c r="AN20" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO20" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP20" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ20" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR20" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS20" s="10" t="inlineStr">
+        <is>
+          <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -48688,6 +49923,36 @@
           <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
         </is>
       </c>
+      <c r="AN21" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO21" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP21" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ21" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR21" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS21" s="10" t="inlineStr">
+        <is>
+          <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -48795,6 +50060,36 @@
           <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
         </is>
       </c>
+      <c r="AN22" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO22" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP22" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ22" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR22" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS22" s="10" t="inlineStr">
+        <is>
+          <t>AUC1-4 h for postprandial glucose (mg · h/dl) 682.8 (91.2) 680.4 (92.2) 658.1 (116.2)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -48902,6 +50197,36 @@
           <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
         </is>
       </c>
+      <c r="AN23" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO23" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP23" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ23" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR23" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS23" s="10" t="inlineStr">
+        <is>
+          <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -49009,6 +50334,36 @@
           <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
         </is>
       </c>
+      <c r="AN24" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO24" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP24" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ24" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR24" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS24" s="10" t="inlineStr">
+        <is>
+          <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -49116,6 +50471,36 @@
           <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
         </is>
       </c>
+      <c r="AN25" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO25" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP25" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ25" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR25" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS25" s="10" t="inlineStr">
+        <is>
+          <t>24-hour mean glucose (mg/dl) 184.1 (30.5) 181.3 (25.9) 178.4 (33.4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -49223,6 +50608,36 @@
           <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
         </is>
       </c>
+      <c r="AN26" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO26" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP26" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ26" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR26" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS26" s="10" t="inlineStr">
+        <is>
+          <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -49330,6 +50745,36 @@
           <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
         </is>
       </c>
+      <c r="AN27" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO27" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP27" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ27" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR27" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS27" s="10" t="inlineStr">
+        <is>
+          <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -49437,6 +50882,36 @@
           <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
         </is>
       </c>
+      <c r="AN28" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO28" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP28" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ28" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR28" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS28" s="10" t="inlineStr">
+        <is>
+          <t>Mean amplitude of glucose excursions, MAGE (mg/dl) 91.4 (26.4) 94.1 (18.5) 89.1 (29.7)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -49544,6 +51019,36 @@
           <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
         </is>
       </c>
+      <c r="AN29" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO29" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP29" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ29" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR29" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS29" s="10" t="inlineStr">
+        <is>
+          <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -49651,6 +51156,36 @@
           <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
         </is>
       </c>
+      <c r="AN30" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO30" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP30" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ30" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR30" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS30" s="10" t="inlineStr">
+        <is>
+          <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -49758,6 +51293,36 @@
           <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
         </is>
       </c>
+      <c r="AN31" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO31" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP31" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ31" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR31" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS31" s="10" t="inlineStr">
+        <is>
+          <t>Estimated glomerular filtration rate (ml/min/1.73 m 2) (Japanese estimation equation [ 27]) 82.6 (12.8) 76.5 (11.1) 80.7 (9.3)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -49865,6 +51430,36 @@
           <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
         </is>
       </c>
+      <c r="AN32" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO32" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP32" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ32" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR32" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS32" s="10" t="inlineStr">
+        <is>
+          <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -49972,6 +51567,36 @@
           <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
         </is>
       </c>
+      <c r="AN33" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO33" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP33" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ33" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR33" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS33" s="10" t="inlineStr">
+        <is>
+          <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -50079,6 +51704,36 @@
           <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
         </is>
       </c>
+      <c r="AN34" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO34" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP34" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ34" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR34" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS34" s="10" t="inlineStr">
+        <is>
+          <t>Systolic blood pressure (mmHg)* 119.8 (11.5) 119.1 (15.9) 124.0 (11.6)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -50186,6 +51841,36 @@
           <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
         </is>
       </c>
+      <c r="AN35" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO35" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP35" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ35" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR35" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS35" s="10" t="inlineStr">
+        <is>
+          <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -50293,6 +51978,36 @@
           <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
         </is>
       </c>
+      <c r="AN36" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO36" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP36" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ36" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR36" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS36" s="10" t="inlineStr">
+        <is>
+          <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -50400,6 +52115,36 @@
           <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
         </is>
       </c>
+      <c r="AN37" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO37" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP37" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ37" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR37" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS37" s="10" t="inlineStr">
+        <is>
+          <t>Diastolic blood pressure (mmHg)* 71.8 (7.7) 70.7 (10.7) 74.7 (8.0)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -50509,6 +52254,36 @@
           <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
         </is>
       </c>
+      <c r="AN38" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO38" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP38" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ38" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR38" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS38" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -50618,6 +52393,36 @@
           <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
         </is>
       </c>
+      <c r="AN39" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO39" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP39" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ39" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR39" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS39" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -50727,6 +52532,36 @@
           <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
         </is>
       </c>
+      <c r="AN40" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO40" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP40" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ40" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR40" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS40" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 66.4 (63.5)* 58.9 (55.6) 65.3 (46.2)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -50844,6 +52679,36 @@
           <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN41" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO41" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP41" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ41" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR41" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS41" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -50975,6 +52840,36 @@
           <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN42" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO42" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP42" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ42" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR42" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS42" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -51106,6 +53001,36 @@
           <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN43" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO43" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP43" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ43" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR43" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS43" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.2 (1.1, 1.3) 1.0 (0.9, 1.1) 1.0 (0.9, 1.0) | Difference vs placebo (95% CI) 0.8 (0.7, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -51223,6 +53148,36 @@
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN44" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO44" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP44" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ44" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR44" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS44" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -51354,6 +53309,36 @@
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN45" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO45" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP45" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ45" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR45" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS45" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -51481,6 +53466,36 @@
         </is>
       </c>
       <c r="AM46" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
+      <c r="AN46" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO46" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP46" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ46" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR46" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS46" s="10" t="inlineStr">
         <is>
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.1) 0.9 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
@@ -51594,6 +53609,36 @@
           <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
         </is>
       </c>
+      <c r="AN47" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO47" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP47" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ47" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR47" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS47" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -51703,6 +53748,36 @@
           <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
         </is>
       </c>
+      <c r="AN48" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO48" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP48" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ48" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR48" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS48" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -51812,6 +53887,36 @@
           <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
         </is>
       </c>
+      <c r="AN49" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO49" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP49" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ49" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR49" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS49" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 73.8 (56.6) † 60.7 (60.5) 70.0 (53.7)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -51929,6 +54034,36 @@
           <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN50" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO50" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP50" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ50" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR50" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS50" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -52060,6 +54195,36 @@
           <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN51" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO51" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP51" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ51" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR51" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS51" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -52191,6 +54356,36 @@
           <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN52" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO52" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP52" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ52" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR52" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS52" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 1 1.1 (1.0, 1.2) 0.9 (0.8, 1.0) 0.9 (0.8, 0.9) | Difference vs placebo (95% CI) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -52308,6 +54503,36 @@
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN53" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO53" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP53" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ53" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR53" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS53" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -52439,6 +54664,36 @@
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
       </c>
+      <c r="AN54" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO54" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP54" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ54" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR54" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS54" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -52566,6 +54821,36 @@
         </is>
       </c>
       <c r="AM55" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
+        </is>
+      </c>
+      <c r="AN55" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO55" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP55" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ55" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR55" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS55" s="10" t="inlineStr">
         <is>
           <t>Relative change from baseline at day 28 1.0 (0.9, 1.0) 0.8 (0.8, 0.9) 0.8 (0.7, 0.9) | Difference vs placebo (95% CI) 0.9 (0.8, 1.0) 0.8 (0.7, 0.9)</t>
         </is>
@@ -52679,6 +54964,36 @@
           <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
         </is>
       </c>
+      <c r="AN56" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO56" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP56" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ56" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR56" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS56" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -52788,6 +55103,36 @@
           <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
         </is>
       </c>
+      <c r="AN57" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO57" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP57" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ57" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR57" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS57" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -52897,6 +55242,36 @@
           <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
         </is>
       </c>
+      <c r="AN58" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO58" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP58" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ58" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR58" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS58" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 197.8 (27.0) 194.6 (29.4) 146.5 (18.5)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -53012,6 +55387,36 @@
           <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
         </is>
       </c>
+      <c r="AN59" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO59" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP59" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ59" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR59" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS59" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -53141,6 +55546,36 @@
           <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
         </is>
       </c>
+      <c r="AN60" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO60" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP60" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ60" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR60" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS60" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -53266,6 +55701,36 @@
         </is>
       </c>
       <c r="AM61" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
+        </is>
+      </c>
+      <c r="AN61" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO61" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP61" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ61" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR61" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS61" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 28 40.6 (22.6) -48.1 (23.3) -33.5 (23.7) | Difference vs placebo (95% CI) -88.6 (-154.6, -22.7) -74.0 (-139.8, -8.2)</t>
         </is>
@@ -53379,6 +55844,36 @@
           <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
         </is>
       </c>
+      <c r="AN62" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO62" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP62" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ62" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR62" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS62" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -53488,6 +55983,36 @@
           <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
         </is>
       </c>
+      <c r="AN63" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO63" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP63" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ63" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR63" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS63" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -53597,6 +56122,36 @@
           <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
         </is>
       </c>
+      <c r="AN64" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO64" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP64" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ64" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR64" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS64" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 115.5 (11.0) 138.3 (20.6) 148.6 (21.7)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -53712,6 +56267,36 @@
           <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
         </is>
       </c>
+      <c r="AN65" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO65" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP65" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ65" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR65" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS65" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -53841,6 +56426,36 @@
           <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
         </is>
       </c>
+      <c r="AN66" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO66" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP66" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ66" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR66" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS66" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -53966,6 +56581,36 @@
         </is>
       </c>
       <c r="AM67" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
+        </is>
+      </c>
+      <c r="AN67" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO67" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP67" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ67" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR67" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS67" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 28 -3.7 (10.3) -28.4 (10.4) -46.8 (10.6) | Difference vs placebo (95% CI) -24.7 (-54.5, 5.2) -43.1 (-72.9, -13.3)</t>
         </is>
@@ -54079,6 +56724,36 @@
           <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
         </is>
       </c>
+      <c r="AN68" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO68" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP68" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ68" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR68" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS68" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -54188,6 +56863,36 @@
           <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
         </is>
       </c>
+      <c r="AN69" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO69" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP69" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ69" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR69" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS69" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -54297,6 +57002,36 @@
           <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
         </is>
       </c>
+      <c r="AN70" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO70" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP70" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ70" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR70" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS70" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 212.8 (7.7) 200.1 (8.4) 208.7 (9.1)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -54412,6 +57147,36 @@
           <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
         </is>
       </c>
+      <c r="AN71" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO71" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP71" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ71" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR71" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS71" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -54541,6 +57306,36 @@
           <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
         </is>
       </c>
+      <c r="AN72" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO72" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP72" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ72" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR72" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS72" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -54666,6 +57461,36 @@
         </is>
       </c>
       <c r="AM73" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
+        </is>
+      </c>
+      <c r="AN73" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO73" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP73" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ73" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR73" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS73" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 29 -0.8 (3.6) 3.2 (3.7) 1.1 (3.7) | Difference vs placebo (95% CI) 4.0 ( -6.6, 14.6) 1.9 ( -8.6, 12.3)</t>
         </is>
@@ -54779,6 +57604,36 @@
           <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
         </is>
       </c>
+      <c r="AN74" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO74" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP74" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ74" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR74" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS74" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -54888,6 +57743,36 @@
           <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
         </is>
       </c>
+      <c r="AN75" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO75" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP75" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ75" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR75" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS75" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -54997,6 +57882,36 @@
           <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
         </is>
       </c>
+      <c r="AN76" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO76" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP76" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ76" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR76" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS76" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 46.8 (2.2) 47.6 (2.8) 46.8 (2.8)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -55112,6 +58027,36 @@
           <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
         </is>
       </c>
+      <c r="AN77" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO77" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP77" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ77" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR77" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS77" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -55241,6 +58186,36 @@
           <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
         </is>
       </c>
+      <c r="AN78" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO78" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP78" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ78" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR78" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS78" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -55366,6 +58341,36 @@
         </is>
       </c>
       <c r="AM79" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
+        </is>
+      </c>
+      <c r="AN79" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO79" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP79" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ79" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR79" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS79" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 29 0.1 (1.2) 4.7 (1.3) 7.4 (1.3) | Difference vs placebo (95% CI) 4.5 (1.0, 8.1) 7.2 (3.7, 10.8)</t>
         </is>
@@ -55479,6 +58484,36 @@
           <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
         </is>
       </c>
+      <c r="AN80" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO80" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP80" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ80" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR80" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS80" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -55588,6 +58623,36 @@
           <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
         </is>
       </c>
+      <c r="AN81" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO81" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP81" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ81" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR81" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS81" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -55697,6 +58762,36 @@
           <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
         </is>
       </c>
+      <c r="AN82" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO82" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP82" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ82" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR82" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS82" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 128.7 (6.3) 124.9 (8.4) 130.5 (8.5)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -55812,6 +58907,36 @@
           <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
         </is>
       </c>
+      <c r="AN83" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO83" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP83" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ83" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR83" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS83" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -55941,6 +59066,36 @@
           <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
         </is>
       </c>
+      <c r="AN84" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO84" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP84" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ84" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR84" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS84" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -56066,6 +59221,36 @@
         </is>
       </c>
       <c r="AM85" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
+        </is>
+      </c>
+      <c r="AN85" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO85" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP85" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ85" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR85" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS85" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 29 -1.3 (3.2) 3.4 (3.3) 4.3 (3.3) | Difference vs placebo (95% CI) 4.7 ( -4.6, 14.0) 5.7 ( -3.5, 14.8)</t>
         </is>
@@ -56179,6 +59364,36 @@
           <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
         </is>
       </c>
+      <c r="AN86" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO86" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP86" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ86" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR86" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS86" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -56288,6 +59503,36 @@
           <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
         </is>
       </c>
+      <c r="AN87" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO87" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP87" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ87" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR87" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS87" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -56397,6 +59642,36 @@
           <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
         </is>
       </c>
+      <c r="AN88" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO88" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN</t>
+        </is>
+      </c>
+      <c r="AP88" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ88" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR88" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS88" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 159.6 (51.0) 131.5 (34.9) 142.2 (48.0)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -56514,6 +59789,36 @@
           <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
         </is>
       </c>
+      <c r="AN89" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO89" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP89" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ89" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR89" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS89" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -56645,6 +59950,36 @@
           <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
         </is>
       </c>
+      <c r="AN90" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO90" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP90" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ90" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR90" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS90" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -56772,6 +60107,36 @@
         </is>
       </c>
       <c r="AM91" s="10" t="inlineStr">
+        <is>
+          <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
+        </is>
+      </c>
+      <c r="AN91" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO91" s="10" t="inlineStr">
+        <is>
+          <t>GEOMETRIC_MEAN_RATIO</t>
+        </is>
+      </c>
+      <c r="AP91" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ91" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR91" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS91" s="10" t="inlineStr">
         <is>
           <t>Relative change from baseline at day 29 1.0 (0.9, 1.1) 0.8 (0.7, 0.9) 0.7 (0.6, 0.8) | Difference vs placebo (95% CI) 0.8 (0.7, 1.0) 0.7 (0.6, 0.8)</t>
         </is>
@@ -56885,6 +60250,36 @@
           <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
         </is>
       </c>
+      <c r="AN92" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO92" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP92" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ92" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR92" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS92" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -56994,6 +60389,36 @@
           <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
         </is>
       </c>
+      <c r="AN93" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO93" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP93" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ93" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR93" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS93" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -57103,6 +60528,36 @@
           <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
         </is>
       </c>
+      <c r="AN94" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO94" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP94" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ94" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR94" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS94" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 10.8 (0.8) 9.6 (0.7) 9.3 (0.6)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -57218,6 +60673,36 @@
           <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
         </is>
       </c>
+      <c r="AN95" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO95" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP95" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ95" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR95" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS95" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -57347,6 +60832,36 @@
           <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
         </is>
       </c>
+      <c r="AN96" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO96" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP96" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ96" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR96" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS96" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -57472,6 +60987,36 @@
         </is>
       </c>
       <c r="AM97" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
+        </is>
+      </c>
+      <c r="AN97" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO97" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP97" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ97" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR97" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS97" s="10" t="inlineStr">
         <is>
           <t>Change from baseline at day 29 3.1 (0.8) 4.8 (0.8) 7.4 (0.8) | Difference vs placebo (95% CI) 1.7 ( -0.6, 4.1) 4.3 (2.0, 6.7)</t>
         </is>
@@ -57585,6 +61130,36 @@
           <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
         </is>
       </c>
+      <c r="AN98" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO98" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP98" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ98" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR98" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS98" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -57694,6 +61269,36 @@
           <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
         </is>
       </c>
+      <c r="AN99" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO99" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP99" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ99" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR99" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS99" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -57803,6 +61408,36 @@
           <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
         </is>
       </c>
+      <c r="AN100" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO100" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_MEAN</t>
+        </is>
+      </c>
+      <c r="AP100" s="10" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="AQ100" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR100" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS100" s="10" t="inlineStr">
+        <is>
+          <t>Baseline 86.8 (10.2) 78.1 (12.0) 69.4 (10.8)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -57918,6 +61553,36 @@
           <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
         </is>
       </c>
+      <c r="AN101" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO101" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP101" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ101" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR101" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS101" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -58047,6 +61712,36 @@
           <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
         </is>
       </c>
+      <c r="AN102" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO102" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP102" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ102" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR102" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS102" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -58176,6 +61871,36 @@
           <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
         </is>
       </c>
+      <c r="AN103" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO103" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP103" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ103" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR103" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS103" s="10" t="inlineStr">
+        <is>
+          <t>Change from baseline at day 29 -12.2 (44.0) 139.5 (44.7) 408.0 (45.5) | Difference vs placebo (95% CI) 151.7 (24.4, 279.0) 420.2 (293.3, 547.2)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -58287,6 +62012,36 @@
           <t>Figure 2A: Placebo at Day 1: Adjusted mean change from baseline 7.9 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN104" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO104" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP104" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ104" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR104" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS104" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Placebo at Day 1: Adjusted mean change from baseline 7.9 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -58398,6 +62153,36 @@
           <t>Figure 2A: Placebo at Day 28: Adjusted mean change from baseline -18.1 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN105" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO105" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP105" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ105" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR105" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS105" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Placebo at Day 28: Adjusted mean change from baseline -18.1 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -58523,6 +62308,36 @@
           <t>Figure 2A: Empagliflozin 10 mg at Day 1: Adjusted mean change from baseline -89.2 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN106" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO106" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP106" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ106" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR106" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS106" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Empagliflozin 10 mg at Day 1: Adjusted mean change from baseline -89.2 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -58648,6 +62463,36 @@
           <t>Figure 2A: Empagliflozin 10 mg at Day 28: Adjusted mean change from baseline -103.6 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN107" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO107" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP107" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ107" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR107" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS107" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Empagliflozin 10 mg at Day 28: Adjusted mean change from baseline -103.6 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -58773,6 +62618,36 @@
           <t>Figure 2A: Empagliflozin 25 mg at Day 1: Adjusted mean change from baseline -83.7 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN108" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO108" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP108" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ108" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR108" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS108" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Empagliflozin 25 mg at Day 1: Adjusted mean change from baseline -83.7 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -58898,6 +62773,36 @@
           <t>Figure 2A: Empagliflozin 25 mg at Day 28: Adjusted mean change from baseline -122.9 mg·h/dL</t>
         </is>
       </c>
+      <c r="AN109" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO109" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP109" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ109" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR109" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS109" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2A: Empagliflozin 25 mg at Day 28: Adjusted mean change from baseline -122.9 mg·h/dL</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -59005,6 +62910,36 @@
           <t>Figure 3: Placebo at Day 2: Adjusted mean change from baseline -4.2 mg/dL</t>
         </is>
       </c>
+      <c r="AN110" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO110" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP110" s="10" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="AQ110" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR110" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS110" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Placebo at Day 2: Adjusted mean change from baseline -4.2 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -59112,6 +63047,36 @@
           <t>Figure 3: Placebo at Day 29: Adjusted mean change from baseline -6.2 mg/dL</t>
         </is>
       </c>
+      <c r="AN111" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO111" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP111" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ111" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR111" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS111" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Placebo at Day 29: Adjusted mean change from baseline -6.2 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -59233,6 +63198,36 @@
           <t>Figure 3: Empagliflozin 10 mg at Day 2: Adjusted mean change from baseline -23.8 mg/dL</t>
         </is>
       </c>
+      <c r="AN112" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO112" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP112" s="10" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="AQ112" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR112" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS112" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Empagliflozin 10 mg at Day 2: Adjusted mean change from baseline -23.8 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -59354,6 +63349,36 @@
           <t>Figure 3: Empagliflozin 10 mg at Day 29: Adjusted mean change from baseline -28.3 mg/dL</t>
         </is>
       </c>
+      <c r="AN113" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO113" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP113" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ113" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR113" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS113" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Empagliflozin 10 mg at Day 29: Adjusted mean change from baseline -28.3 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -59475,6 +63500,36 @@
           <t>Figure 3: Empagliflozin 25 mg at Day 2: Adjusted mean change from baseline -30.5 mg/dL</t>
         </is>
       </c>
+      <c r="AN114" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO114" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP114" s="10" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="AQ114" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR114" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS114" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Empagliflozin 25 mg at Day 2: Adjusted mean change from baseline -30.5 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -59596,6 +63651,36 @@
           <t>Figure 3: Empagliflozin 25 mg at Day 29: Adjusted mean change from baseline -39.7 mg/dL</t>
         </is>
       </c>
+      <c r="AN115" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO115" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP115" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ115" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR115" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS115" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: Empagliflozin 25 mg at Day 29: Adjusted mean change from baseline -39.7 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -59703,6 +63788,36 @@
           <t>Figure 4: Placebo at Day 1: Adjusted mean change from baseline 0.3 mg/dL</t>
         </is>
       </c>
+      <c r="AN116" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO116" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP116" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ116" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR116" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS116" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Placebo at Day 1: Adjusted mean change from baseline 0.3 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -59810,6 +63925,36 @@
           <t>Figure 4: Placebo at Day 28: Adjusted mean change from baseline -5.8 mg/dL</t>
         </is>
       </c>
+      <c r="AN117" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO117" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP117" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ117" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR117" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS117" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Placebo at Day 28: Adjusted mean change from baseline -5.8 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -59931,6 +64076,36 @@
           <t>Figure 4: Empagliflozin 10 mg at Day 1: Adjusted mean change from baseline -20.5 mg/dL</t>
         </is>
       </c>
+      <c r="AN118" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO118" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP118" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ118" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR118" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS118" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Empagliflozin 10 mg at Day 1: Adjusted mean change from baseline -20.5 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -60052,6 +64227,36 @@
           <t>Figure 4: Empagliflozin 10 mg at Day 28: Adjusted mean change from baseline -30.3 mg/dL</t>
         </is>
       </c>
+      <c r="AN119" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO119" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP119" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ119" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR119" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS119" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Empagliflozin 10 mg at Day 28: Adjusted mean change from baseline -30.3 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -60173,6 +64378,36 @@
           <t>Figure 4: Empagliflozin 25 mg at Day 1: Adjusted mean change from baseline -23.6 mg/dL</t>
         </is>
       </c>
+      <c r="AN120" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO120" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP120" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ120" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR120" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS120" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Empagliflozin 25 mg at Day 1: Adjusted mean change from baseline -23.6 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -60294,6 +64529,36 @@
           <t>Figure 4: Empagliflozin 25 mg at Day 28: Adjusted mean change from baseline -37.6 mg/dL</t>
         </is>
       </c>
+      <c r="AN121" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO121" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP121" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ121" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR121" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS121" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: Empagliflozin 25 mg at Day 28: Adjusted mean change from baseline -37.6 mg/dL</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -60405,6 +64670,36 @@
           <t>Results Section 3.2: Placebo at Day 1: MAGE change from baseline 15.1 mg/dL (SE 3.5)</t>
         </is>
       </c>
+      <c r="AN122" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO122" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP122" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ122" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR122" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS122" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Placebo at Day 1: MAGE change from baseline 15.1 mg/dL (SE 3.5)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -60516,6 +64811,36 @@
           <t>Results Section 3.2: Placebo at Day 28: MAGE change from baseline -4.7 mg/dL (SE 4.5)</t>
         </is>
       </c>
+      <c r="AN123" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO123" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP123" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ123" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR123" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS123" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Placebo at Day 28: MAGE change from baseline -4.7 mg/dL (SE 4.5)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -60627,6 +64952,36 @@
           <t>Results Section 3.2: Empagliflozin 10 mg at Day 1: MAGE change from baseline 11.0 mg/dL (SE 3.7)</t>
         </is>
       </c>
+      <c r="AN124" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO124" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP124" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ124" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR124" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS124" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 10 mg at Day 1: MAGE change from baseline 11.0 mg/dL (SE 3.7)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -60738,6 +65093,36 @@
           <t>Results Section 3.2: Empagliflozin 10 mg at Day 28: MAGE change from baseline -3.7 mg/dL (SE 4.6)</t>
         </is>
       </c>
+      <c r="AN125" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO125" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP125" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ125" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR125" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS125" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 10 mg at Day 28: MAGE change from baseline -3.7 mg/dL (SE 4.6)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -60849,6 +65234,36 @@
           <t>Results Section 3.2: Empagliflozin 25 mg at Day 1: MAGE change from baseline 8.9 mg/dL (SE 3.7)</t>
         </is>
       </c>
+      <c r="AN126" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO126" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP126" s="10" t="inlineStr">
+        <is>
+          <t>1 days</t>
+        </is>
+      </c>
+      <c r="AQ126" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR126" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS126" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 25 mg at Day 1: MAGE change from baseline 8.9 mg/dL (SE 3.7)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -60960,6 +65375,36 @@
           <t>Results Section 3.2: Empagliflozin 25 mg at Day 28: MAGE change from baseline -2.2 mg/dL (SE 4.7)</t>
         </is>
       </c>
+      <c r="AN127" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO127" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP127" s="10" t="inlineStr">
+        <is>
+          <t>28 days</t>
+        </is>
+      </c>
+      <c r="AQ127" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR127" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS127" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 25 mg at Day 28: MAGE change from baseline -2.2 mg/dL (SE 4.7)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -61071,6 +65516,36 @@
           <t>Results Section 3.2: Placebo at Day 29: HbA1c change from baseline -0.11% (SE 0.06)</t>
         </is>
       </c>
+      <c r="AN128" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO128" s="10" t="inlineStr">
+        <is>
+          <t>RAW_CHANGE_FROM_BASELINE</t>
+        </is>
+      </c>
+      <c r="AP128" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ128" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR128" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS128" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Placebo at Day 29: HbA1c change from baseline -0.11% (SE 0.06)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -61196,6 +65671,36 @@
           <t>Results Section 3.2: Empagliflozin 10 mg at Day 29: HbA1c change from baseline -0.46% (SE 0.06)</t>
         </is>
       </c>
+      <c r="AN129" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO129" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP129" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ129" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR129" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS129" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 10 mg at Day 29: HbA1c change from baseline -0.46% (SE 0.06)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -61321,6 +65826,36 @@
           <t>Results Section 3.2: Empagliflozin 25 mg at Day 29: HbA1c change from baseline -0.63% (SE 0.06)</t>
         </is>
       </c>
+      <c r="AN130" s="10" t="inlineStr">
+        <is>
+          <t>EFFICACY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO130" s="10" t="inlineStr">
+        <is>
+          <t>ADJUSTED_MEAN_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="AP130" s="10" t="inlineStr">
+        <is>
+          <t>29 days</t>
+        </is>
+      </c>
+      <c r="AQ130" s="10" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="AR130" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS130" s="10" t="inlineStr">
+        <is>
+          <t>Results Section 3.2: Empagliflozin 25 mg at Day 29: HbA1c change from baseline -0.63% (SE 0.06)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -61354,7 +65889,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>any adverse event</t>
+          <t>Any Adverse Event</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -61430,6 +65965,36 @@
           <t>Any Adverse Event: 2 (9.5%)</t>
         </is>
       </c>
+      <c r="AN131" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO131" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP131" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ131" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR131" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS131" s="10" t="inlineStr">
+        <is>
+          <t>Any Adverse Event: 2 (9.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
@@ -61463,7 +66028,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>any adverse event</t>
+          <t>Any Adverse Event</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -61539,6 +66104,36 @@
           <t>Any Adverse Event: 3 (15.0%)</t>
         </is>
       </c>
+      <c r="AN132" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO132" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP132" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ132" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR132" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS132" s="10" t="inlineStr">
+        <is>
+          <t>Any Adverse Event: 3 (15.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -61572,7 +66167,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>any adverse event</t>
+          <t>Any Adverse Event</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -61648,6 +66243,36 @@
           <t>Any Adverse Event: 3 (15.8%)</t>
         </is>
       </c>
+      <c r="AN133" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO133" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP133" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ133" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR133" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS133" s="10" t="inlineStr">
+        <is>
+          <t>Any Adverse Event: 3 (15.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -61757,6 +66382,36 @@
           <t>Severe Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN134" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO134" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP134" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ134" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR134" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS134" s="10" t="inlineStr">
+        <is>
+          <t>Severe Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
@@ -61866,6 +66521,36 @@
           <t>Severe Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN135" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO135" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP135" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ135" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR135" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS135" s="10" t="inlineStr">
+        <is>
+          <t>Severe Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
@@ -61975,6 +66660,36 @@
           <t>Severe Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN136" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO136" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP136" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ136" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR136" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS136" s="10" t="inlineStr">
+        <is>
+          <t>Severe Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
@@ -62084,6 +66799,36 @@
           <t>Serious Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN137" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO137" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP137" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ137" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR137" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS137" s="10" t="inlineStr">
+        <is>
+          <t>Serious Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
@@ -62193,6 +66938,36 @@
           <t>Serious Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN138" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO138" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP138" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ138" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR138" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS138" s="10" t="inlineStr">
+        <is>
+          <t>Serious Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -62302,6 +67077,36 @@
           <t>Serious Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN139" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO139" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP139" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ139" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR139" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS139" s="10" t="inlineStr">
+        <is>
+          <t>Serious Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -62411,6 +67216,36 @@
           <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN140" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO140" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP140" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ140" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR140" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS140" s="10" t="inlineStr">
+        <is>
+          <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -62520,6 +67355,36 @@
           <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN141" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO141" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP141" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ141" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR141" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS141" s="10" t="inlineStr">
+        <is>
+          <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -62629,6 +67494,36 @@
           <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN142" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO142" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP142" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ142" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR142" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS142" s="10" t="inlineStr">
+        <is>
+          <t>Discontinuation Due to Adverse Events: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -62738,6 +67633,36 @@
           <t>Hypoglycemia: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN143" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO143" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP143" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ143" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR143" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS143" s="10" t="inlineStr">
+        <is>
+          <t>Hypoglycemia: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -62847,6 +67772,36 @@
           <t>Hypoglycemia: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN144" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO144" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP144" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ144" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR144" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS144" s="10" t="inlineStr">
+        <is>
+          <t>Hypoglycemia: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -62956,6 +67911,36 @@
           <t>Hypoglycemia: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN145" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO145" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP145" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ145" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR145" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS145" s="10" t="inlineStr">
+        <is>
+          <t>Hypoglycemia: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -63065,6 +68050,36 @@
           <t>Genital Infection: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN146" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO146" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP146" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ146" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR146" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS146" s="10" t="inlineStr">
+        <is>
+          <t>Genital Infection: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -63174,6 +68189,36 @@
           <t>Genital Infection: 0 (0.0%)</t>
         </is>
       </c>
+      <c r="AN147" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO147" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP147" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ147" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR147" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS147" s="10" t="inlineStr">
+        <is>
+          <t>Genital Infection: 0 (0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
@@ -63283,6 +68328,36 @@
           <t>Genital Infection: 1 (5.3%)</t>
         </is>
       </c>
+      <c r="AN148" s="10" t="inlineStr">
+        <is>
+          <t>SAFETY_OUTCOME</t>
+        </is>
+      </c>
+      <c r="AO148" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP148" s="10" t="inlineStr">
+        <is>
+          <t>Safety observation period</t>
+        </is>
+      </c>
+      <c r="AQ148" s="10" t="inlineStr">
+        <is>
+          <t>overall_safety_period</t>
+        </is>
+      </c>
+      <c r="AR148" s="10" t="inlineStr">
+        <is>
+          <t>cumulative_period</t>
+        </is>
+      </c>
+      <c r="AS148" s="10" t="inlineStr">
+        <is>
+          <t>Genital Infection: 1 (5.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
@@ -63392,6 +68467,36 @@
           <t>Female Count = Total N (21) - Male Count (17)</t>
         </is>
       </c>
+      <c r="AN149" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO149" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP149" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ149" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR149" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS149" s="10" t="inlineStr">
+        <is>
+          <t>Female Count = Total N (21) - Male Count (17)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
@@ -63501,6 +68606,36 @@
           <t>Female Count = Total N (20) - Male Count (14)</t>
         </is>
       </c>
+      <c r="AN150" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO150" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP150" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ150" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR150" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS150" s="10" t="inlineStr">
+        <is>
+          <t>Female Count = Total N (20) - Male Count (14)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
@@ -63610,6 +68745,36 @@
           <t>Female Count = Total N (19) - Male Count (16)</t>
         </is>
       </c>
+      <c r="AN151" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO151" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP151" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ151" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR151" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS151" s="10" t="inlineStr">
+        <is>
+          <t>Female Count = Total N (19) - Male Count (16)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
@@ -63715,6 +68880,36 @@
           <t>All 21 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
         </is>
       </c>
+      <c r="AN152" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO152" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP152" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ152" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR152" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS152" s="10" t="inlineStr">
+        <is>
+          <t>All 21 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
@@ -63820,6 +69015,36 @@
           <t>All 20 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
         </is>
       </c>
+      <c r="AN153" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO153" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP153" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ153" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR153" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS153" s="10" t="inlineStr">
+        <is>
+          <t>All 20 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
@@ -63921,6 +69146,36 @@
         </is>
       </c>
       <c r="AM154" s="10" t="inlineStr">
+        <is>
+          <t>All 19 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
+        </is>
+      </c>
+      <c r="AN154" s="10" t="inlineStr">
+        <is>
+          <t>BASELINE_CHARACTERISTIC</t>
+        </is>
+      </c>
+      <c r="AO154" s="10" t="inlineStr">
+        <is>
+          <t>BINARY_RATE</t>
+        </is>
+      </c>
+      <c r="AP154" s="10" t="inlineStr">
+        <is>
+          <t>0 weeks</t>
+        </is>
+      </c>
+      <c r="AQ154" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="AR154" s="10" t="inlineStr">
+        <is>
+          <t>point_in_time</t>
+        </is>
+      </c>
+      <c r="AS154" s="10" t="inlineStr">
         <is>
           <t>All 19 participants were Asian (Japanese) (100.0%) as stated in Title, Abstract, and Study Aim</t>
         </is>
@@ -64267,6 +69522,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -67623,6 +72879,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
